--- a/research/traditional_assets/database/data/france/france_trucking.xlsx
+++ b/research/traditional_assets/database/data/france/france_trucking.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08826933483635638</v>
+        <v>0.08808241149926549</v>
       </c>
       <c r="C2">
-        <v>2754.898514909239</v>
+        <v>2734.327369923412</v>
       </c>
       <c r="D2">
-        <v>2603.098514909238</v>
+        <v>2614.606369923412</v>
       </c>
       <c r="E2">
-        <v>-1539.8</v>
+        <v>-1507.721</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32.07899999999999</v>
       </c>
       <c r="G2">
         <v>151.8</v>
@@ -1451,28 +1451,28 @@
         <v>171.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.6135737</v>
       </c>
       <c r="N2">
-        <v>171.2</v>
+        <v>169.5864263</v>
       </c>
       <c r="O2">
-        <v>42.8</v>
+        <v>42.396606575</v>
       </c>
       <c r="P2">
-        <v>128.4</v>
+        <v>127.189819725</v>
       </c>
       <c r="Q2">
-        <v>364.1</v>
+        <v>362.889819725</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08826933483635638</v>
+        <v>0.0885910722214803</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919478</v>
+        <v>0.8340776445774929</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>106.0998949102852</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08808241149926549</v>
+        <v>0.08789548816217461</v>
       </c>
       <c r="C3">
-        <v>2734.327369923412</v>
+        <v>2713.858425280468</v>
       </c>
       <c r="D3">
-        <v>2614.606369923412</v>
+        <v>2626.216425280468</v>
       </c>
       <c r="E3">
-        <v>-1507.721</v>
+        <v>-1475.642</v>
       </c>
       <c r="F3">
-        <v>32.07899999999999</v>
+        <v>64.15799999999999</v>
       </c>
       <c r="G3">
         <v>151.8</v>
@@ -1533,28 +1533,28 @@
         <v>171.2</v>
       </c>
       <c r="M3">
-        <v>1.6135737</v>
+        <v>3.227147399999999</v>
       </c>
       <c r="N3">
-        <v>169.5864263</v>
+        <v>167.9728526</v>
       </c>
       <c r="O3">
-        <v>42.396606575</v>
+        <v>41.99321315</v>
       </c>
       <c r="P3">
-        <v>127.189819725</v>
+        <v>125.97963945</v>
       </c>
       <c r="Q3">
-        <v>362.889819725</v>
+        <v>361.67963945</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0885910722214803</v>
+        <v>0.08891937567568838</v>
       </c>
       <c r="T3">
-        <v>0.8340776445774929</v>
+        <v>0.8404768899709063</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>106.0998949102852</v>
+        <v>53.04994745514259</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08789548816217461</v>
+        <v>0.08770856482508371</v>
       </c>
       <c r="C4">
-        <v>2713.858425280468</v>
+        <v>2693.493048502482</v>
       </c>
       <c r="D4">
-        <v>2626.216425280468</v>
+        <v>2637.930048502482</v>
       </c>
       <c r="E4">
-        <v>-1475.642</v>
+        <v>-1443.563</v>
       </c>
       <c r="F4">
-        <v>64.15799999999999</v>
+        <v>96.23699999999998</v>
       </c>
       <c r="G4">
         <v>151.8</v>
@@ -1615,28 +1615,28 @@
         <v>171.2</v>
       </c>
       <c r="M4">
-        <v>3.227147399999999</v>
+        <v>4.840721099999999</v>
       </c>
       <c r="N4">
-        <v>167.9728526</v>
+        <v>166.3592789</v>
       </c>
       <c r="O4">
-        <v>41.99321315</v>
+        <v>41.589819725</v>
       </c>
       <c r="P4">
-        <v>125.97963945</v>
+        <v>124.769459175</v>
       </c>
       <c r="Q4">
-        <v>361.67963945</v>
+        <v>360.469459175</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08891937567568838</v>
+        <v>0.08925444827328217</v>
       </c>
       <c r="T4">
-        <v>0.8404768899709063</v>
+        <v>0.8470080785683074</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>53.04994745514259</v>
+        <v>35.36663163676173</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08770856482508371</v>
+        <v>0.08752164148799281</v>
       </c>
       <c r="C5">
-        <v>2693.493048502482</v>
+        <v>2673.232631618881</v>
       </c>
       <c r="D5">
-        <v>2637.930048502482</v>
+        <v>2649.748631618881</v>
       </c>
       <c r="E5">
-        <v>-1443.563</v>
+        <v>-1411.484</v>
       </c>
       <c r="F5">
-        <v>96.23699999999998</v>
+        <v>128.316</v>
       </c>
       <c r="G5">
         <v>151.8</v>
@@ -1697,28 +1697,28 @@
         <v>171.2</v>
       </c>
       <c r="M5">
-        <v>4.840721099999999</v>
+        <v>6.454294799999999</v>
       </c>
       <c r="N5">
-        <v>166.3592789</v>
+        <v>164.7457052</v>
       </c>
       <c r="O5">
-        <v>41.589819725</v>
+        <v>41.1864263</v>
       </c>
       <c r="P5">
-        <v>124.769459175</v>
+        <v>123.5592789</v>
       </c>
       <c r="Q5">
-        <v>360.469459175</v>
+        <v>359.2592789</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08925444827328217</v>
+        <v>0.08959650154999252</v>
       </c>
       <c r="T5">
-        <v>0.8470080785683074</v>
+        <v>0.8536753335948212</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>35.36663163676173</v>
+        <v>26.5249737275713</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08752164148799281</v>
+        <v>0.08733471815090194</v>
       </c>
       <c r="C6">
-        <v>2673.232631618881</v>
+        <v>2653.078591717916</v>
       </c>
       <c r="D6">
-        <v>2649.748631618881</v>
+        <v>2661.673591717916</v>
       </c>
       <c r="E6">
-        <v>-1411.484</v>
+        <v>-1379.405</v>
       </c>
       <c r="F6">
-        <v>128.316</v>
+        <v>160.395</v>
       </c>
       <c r="G6">
         <v>151.8</v>
@@ -1779,28 +1779,28 @@
         <v>171.2</v>
       </c>
       <c r="M6">
-        <v>6.454294799999999</v>
+        <v>8.067868499999999</v>
       </c>
       <c r="N6">
-        <v>164.7457052</v>
+        <v>163.1321315</v>
       </c>
       <c r="O6">
-        <v>41.1864263</v>
+        <v>40.783032875</v>
       </c>
       <c r="P6">
-        <v>123.5592789</v>
+        <v>122.349098625</v>
       </c>
       <c r="Q6">
-        <v>359.2592789</v>
+        <v>358.0490986249999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08959650154999252</v>
+        <v>0.08994575594831783</v>
       </c>
       <c r="T6">
-        <v>0.8536753335948212</v>
+        <v>0.8604829518850511</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.5249737275713</v>
+        <v>21.21997898205703</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08733471815090194</v>
+        <v>0.08714779481381103</v>
       </c>
       <c r="C7">
-        <v>2653.078591717916</v>
+        <v>2633.03237151309</v>
       </c>
       <c r="D7">
-        <v>2661.673591717916</v>
+        <v>2673.70637151309</v>
       </c>
       <c r="E7">
-        <v>-1379.405</v>
+        <v>-1347.326</v>
       </c>
       <c r="F7">
-        <v>160.395</v>
+        <v>192.474</v>
       </c>
       <c r="G7">
         <v>151.8</v>
@@ -1861,28 +1861,28 @@
         <v>171.2</v>
       </c>
       <c r="M7">
-        <v>8.067868499999999</v>
+        <v>9.681442199999999</v>
       </c>
       <c r="N7">
-        <v>163.1321315</v>
+        <v>161.5185578</v>
       </c>
       <c r="O7">
-        <v>40.783032875</v>
+        <v>40.37963945</v>
       </c>
       <c r="P7">
-        <v>122.349098625</v>
+        <v>121.13891835</v>
       </c>
       <c r="Q7">
-        <v>358.0490986249999</v>
+        <v>356.83891835</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08994575594831783</v>
+        <v>0.09030244129128834</v>
       </c>
       <c r="T7">
-        <v>0.8604829518850511</v>
+        <v>0.8674354131176262</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.21997898205703</v>
+        <v>17.68331581838086</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08714779481381103</v>
+        <v>0.08696087147672014</v>
       </c>
       <c r="C8">
-        <v>2633.03237151309</v>
+        <v>2613.095439925006</v>
       </c>
       <c r="D8">
-        <v>2673.70637151309</v>
+        <v>2685.848439925006</v>
       </c>
       <c r="E8">
-        <v>-1347.326</v>
+        <v>-1315.247</v>
       </c>
       <c r="F8">
-        <v>192.474</v>
+        <v>224.5529999999999</v>
       </c>
       <c r="G8">
         <v>151.8</v>
@@ -1943,28 +1943,28 @@
         <v>171.2</v>
       </c>
       <c r="M8">
-        <v>9.681442199999998</v>
+        <v>11.2950159</v>
       </c>
       <c r="N8">
-        <v>161.5185578</v>
+        <v>159.9049841</v>
       </c>
       <c r="O8">
-        <v>40.37963945</v>
+        <v>39.97624602499999</v>
       </c>
       <c r="P8">
-        <v>121.13891835</v>
+        <v>119.928738075</v>
       </c>
       <c r="Q8">
-        <v>356.83891835</v>
+        <v>355.628738075</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09030244129128834</v>
+        <v>0.09066679728679586</v>
       </c>
       <c r="T8">
-        <v>0.8674354131176262</v>
+        <v>0.8745373896455255</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.68331581838087</v>
+        <v>15.15712784432645</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08696087147672014</v>
+        <v>0.08677394813962927</v>
       </c>
       <c r="C9">
-        <v>2613.095439925006</v>
+        <v>2593.269292679157</v>
       </c>
       <c r="D9">
-        <v>2685.848439925006</v>
+        <v>2698.101292679157</v>
       </c>
       <c r="E9">
-        <v>-1315.247</v>
+        <v>-1283.168</v>
       </c>
       <c r="F9">
-        <v>224.553</v>
+        <v>256.6319999999999</v>
       </c>
       <c r="G9">
         <v>151.8</v>
@@ -2025,28 +2025,28 @@
         <v>171.2</v>
       </c>
       <c r="M9">
-        <v>11.2950159</v>
+        <v>12.9085896</v>
       </c>
       <c r="N9">
-        <v>159.9049841</v>
+        <v>158.2914104</v>
       </c>
       <c r="O9">
-        <v>39.97624602499999</v>
+        <v>39.5728526</v>
       </c>
       <c r="P9">
-        <v>119.928738075</v>
+        <v>118.7185578</v>
       </c>
       <c r="Q9">
-        <v>355.628738075</v>
+        <v>354.4185578</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09066679728679586</v>
+        <v>0.09103907406481442</v>
       </c>
       <c r="T9">
-        <v>0.8745373896455255</v>
+        <v>0.8817937569675097</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.15712784432645</v>
+        <v>13.26248686378565</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08677394813962927</v>
+        <v>0.08668827480253838</v>
       </c>
       <c r="C10">
-        <v>2593.269292679157</v>
+        <v>2566.843633219187</v>
       </c>
       <c r="D10">
-        <v>2698.101292679157</v>
+        <v>2703.754633219187</v>
       </c>
       <c r="E10">
-        <v>-1283.168</v>
+        <v>-1251.089</v>
       </c>
       <c r="F10">
-        <v>256.6319999999999</v>
+        <v>288.711</v>
       </c>
       <c r="G10">
         <v>151.8</v>
@@ -2107,45 +2107,45 @@
         <v>171.2</v>
       </c>
       <c r="M10">
-        <v>12.9085896</v>
+        <v>14.9552298</v>
       </c>
       <c r="N10">
-        <v>158.2914104</v>
+        <v>156.2447702</v>
       </c>
       <c r="O10">
-        <v>39.5728526</v>
+        <v>39.06119255</v>
       </c>
       <c r="P10">
-        <v>118.7185578</v>
+        <v>117.18357765</v>
       </c>
       <c r="Q10">
-        <v>354.4185578</v>
+        <v>352.88357765</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09103907406481442</v>
+        <v>0.09141953275004217</v>
       </c>
       <c r="T10">
-        <v>0.8817937569675097</v>
+        <v>0.8892096048899769</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.26248686378565</v>
+        <v>11.44750045900331</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08668827480253838</v>
+        <v>0.08651260146544748</v>
       </c>
       <c r="C11">
-        <v>2566.843633219187</v>
+        <v>2546.431232306345</v>
       </c>
       <c r="D11">
-        <v>2703.754633219187</v>
+        <v>2715.421232306344</v>
       </c>
       <c r="E11">
-        <v>-1251.089</v>
+        <v>-1219.01</v>
       </c>
       <c r="F11">
-        <v>288.711</v>
+        <v>320.79</v>
       </c>
       <c r="G11">
         <v>151.8</v>
@@ -2189,28 +2189,28 @@
         <v>171.2</v>
       </c>
       <c r="M11">
-        <v>14.9552298</v>
+        <v>16.616922</v>
       </c>
       <c r="N11">
-        <v>156.2447702</v>
+        <v>154.583078</v>
       </c>
       <c r="O11">
-        <v>39.06119255</v>
+        <v>38.6457695</v>
       </c>
       <c r="P11">
-        <v>117.18357765</v>
+        <v>115.9373085</v>
       </c>
       <c r="Q11">
-        <v>352.88357765</v>
+        <v>351.6373085</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09141953275004217</v>
+        <v>0.09180844607271942</v>
       </c>
       <c r="T11">
-        <v>0.8892096048899769</v>
+        <v>0.8967902494329434</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.44750045900331</v>
+        <v>10.30275041310298</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08651260146544748</v>
+        <v>0.08647717812835658</v>
       </c>
       <c r="C12">
-        <v>2546.431232306345</v>
+        <v>2516.716931286993</v>
       </c>
       <c r="D12">
-        <v>2715.421232306344</v>
+        <v>2717.785931286993</v>
       </c>
       <c r="E12">
-        <v>-1219.01</v>
+        <v>-1186.931</v>
       </c>
       <c r="F12">
-        <v>320.79</v>
+        <v>352.869</v>
       </c>
       <c r="G12">
         <v>151.8</v>
@@ -2271,45 +2271,45 @@
         <v>171.2</v>
       </c>
       <c r="M12">
-        <v>16.616922</v>
+        <v>18.8784915</v>
       </c>
       <c r="N12">
-        <v>154.583078</v>
+        <v>152.3215085</v>
       </c>
       <c r="O12">
-        <v>38.6457695</v>
+        <v>38.080377125</v>
       </c>
       <c r="P12">
-        <v>115.9373085</v>
+        <v>114.241131375</v>
       </c>
       <c r="Q12">
-        <v>351.6373085</v>
+        <v>349.941131375</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09180844607271942</v>
+        <v>0.09220609902062538</v>
       </c>
       <c r="T12">
-        <v>0.8967902494329434</v>
+        <v>0.9045412455386734</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.30275041310298</v>
+        <v>9.068521179247822</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08647717812835658</v>
+        <v>0.0863142547912657</v>
       </c>
       <c r="C13">
-        <v>2516.716931286993</v>
+        <v>2495.567189537089</v>
       </c>
       <c r="D13">
-        <v>2717.785931286993</v>
+        <v>2728.715189537088</v>
       </c>
       <c r="E13">
-        <v>-1186.931</v>
+        <v>-1154.852</v>
       </c>
       <c r="F13">
-        <v>352.869</v>
+        <v>384.9479999999999</v>
       </c>
       <c r="G13">
         <v>151.8</v>
@@ -2353,28 +2353,28 @@
         <v>171.2</v>
       </c>
       <c r="M13">
-        <v>18.8784915</v>
+        <v>20.594718</v>
       </c>
       <c r="N13">
-        <v>152.3215085</v>
+        <v>150.605282</v>
       </c>
       <c r="O13">
-        <v>38.080377125</v>
+        <v>37.6513205</v>
       </c>
       <c r="P13">
-        <v>114.241131375</v>
+        <v>112.9539615</v>
       </c>
       <c r="Q13">
-        <v>349.941131375</v>
+        <v>348.6539615</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09220609902062538</v>
+        <v>0.09261278953552921</v>
       </c>
       <c r="T13">
-        <v>0.9045412455386734</v>
+        <v>0.9124684006468061</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.068521179247822</v>
+        <v>8.312811080977172</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0863142547912657</v>
+        <v>0.08615133145417482</v>
       </c>
       <c r="C14">
-        <v>2495.567189537089</v>
+        <v>2474.505704167426</v>
       </c>
       <c r="D14">
-        <v>2728.715189537088</v>
+        <v>2739.732704167426</v>
       </c>
       <c r="E14">
-        <v>-1154.852</v>
+        <v>-1122.773</v>
       </c>
       <c r="F14">
-        <v>384.9479999999999</v>
+        <v>417.027</v>
       </c>
       <c r="G14">
         <v>151.8</v>
@@ -2435,28 +2435,28 @@
         <v>171.2</v>
       </c>
       <c r="M14">
-        <v>20.594718</v>
+        <v>22.3109445</v>
       </c>
       <c r="N14">
-        <v>150.605282</v>
+        <v>148.8890555</v>
       </c>
       <c r="O14">
-        <v>37.6513205</v>
+        <v>37.222263875</v>
       </c>
       <c r="P14">
-        <v>112.9539615</v>
+        <v>111.666791625</v>
       </c>
       <c r="Q14">
-        <v>348.6539615</v>
+        <v>347.366791625</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09261278953552921</v>
+        <v>0.0930288292576722</v>
       </c>
       <c r="T14">
-        <v>0.9124684006468061</v>
+        <v>0.9205777892057005</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.312811080977172</v>
+        <v>7.673364074748157</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08615133145417482</v>
+        <v>0.08607240811708392</v>
       </c>
       <c r="C15">
-        <v>2474.505704167426</v>
+        <v>2447.795860318241</v>
       </c>
       <c r="D15">
-        <v>2739.732704167426</v>
+        <v>2745.101860318241</v>
       </c>
       <c r="E15">
-        <v>-1122.773</v>
+        <v>-1090.694</v>
       </c>
       <c r="F15">
-        <v>417.027</v>
+        <v>449.106</v>
       </c>
       <c r="G15">
         <v>151.8</v>
@@ -2517,45 +2517,45 @@
         <v>171.2</v>
       </c>
       <c r="M15">
-        <v>22.3109445</v>
+        <v>24.3864558</v>
       </c>
       <c r="N15">
-        <v>148.8890555</v>
+        <v>146.8135442</v>
       </c>
       <c r="O15">
-        <v>37.222263875</v>
+        <v>36.70338605</v>
       </c>
       <c r="P15">
-        <v>111.666791625</v>
+        <v>110.11015815</v>
       </c>
       <c r="Q15">
-        <v>347.366791625</v>
+        <v>345.81015815</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0930288292576722</v>
+        <v>0.09345454432219061</v>
       </c>
       <c r="T15">
-        <v>0.9205777892057005</v>
+        <v>0.9288757681961973</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.673364074748157</v>
+        <v>7.020290336736837</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08607240811708392</v>
+        <v>0.08591548477999301</v>
       </c>
       <c r="C16">
-        <v>2447.795860318241</v>
+        <v>2426.455121289985</v>
       </c>
       <c r="D16">
-        <v>2745.101860318241</v>
+        <v>2755.840121289984</v>
       </c>
       <c r="E16">
-        <v>-1090.694</v>
+        <v>-1058.615</v>
       </c>
       <c r="F16">
-        <v>449.106</v>
+        <v>481.185</v>
       </c>
       <c r="G16">
         <v>151.8</v>
@@ -2599,28 +2599,28 @@
         <v>171.2</v>
       </c>
       <c r="M16">
-        <v>24.3864558</v>
+        <v>26.1283455</v>
       </c>
       <c r="N16">
-        <v>146.8135442</v>
+        <v>145.0716545</v>
       </c>
       <c r="O16">
-        <v>36.70338605</v>
+        <v>36.267913625</v>
       </c>
       <c r="P16">
-        <v>110.11015815</v>
+        <v>108.803740875</v>
       </c>
       <c r="Q16">
-        <v>345.81015815</v>
+        <v>344.5037408749999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09345454432219061</v>
+        <v>0.0938902762117565</v>
       </c>
       <c r="T16">
-        <v>0.9288757681961973</v>
+        <v>0.9373689937511762</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.020290336736837</v>
+        <v>6.552270980954381</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08591548477999301</v>
+        <v>0.08575856144290211</v>
       </c>
       <c r="C17">
-        <v>2426.455121289985</v>
+        <v>2405.198723823856</v>
       </c>
       <c r="D17">
-        <v>2755.840121289984</v>
+        <v>2766.662723823856</v>
       </c>
       <c r="E17">
-        <v>-1058.615</v>
+        <v>-1026.536</v>
       </c>
       <c r="F17">
-        <v>481.1849999999999</v>
+        <v>513.2639999999999</v>
       </c>
       <c r="G17">
         <v>151.8</v>
@@ -2681,28 +2681,28 @@
         <v>171.2</v>
       </c>
       <c r="M17">
-        <v>26.1283455</v>
+        <v>27.8702352</v>
       </c>
       <c r="N17">
-        <v>145.0716545</v>
+        <v>143.3297648</v>
       </c>
       <c r="O17">
-        <v>36.267913625</v>
+        <v>35.8324412</v>
       </c>
       <c r="P17">
-        <v>108.803740875</v>
+        <v>107.4973236</v>
       </c>
       <c r="Q17">
-        <v>344.5037408749999</v>
+        <v>343.1973236</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0938902762117565</v>
+        <v>0.09433638267012158</v>
       </c>
       <c r="T17">
-        <v>0.9373689937511762</v>
+        <v>0.946064438962226</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.552270980954382</v>
+        <v>6.142754044644733</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08575856144290211</v>
+        <v>0.08572913810581123</v>
       </c>
       <c r="C18">
-        <v>2405.198723823856</v>
+        <v>2375.158446766589</v>
       </c>
       <c r="D18">
-        <v>2766.662723823856</v>
+        <v>2768.701446766589</v>
       </c>
       <c r="E18">
-        <v>-1026.536</v>
+        <v>-994.457</v>
       </c>
       <c r="F18">
-        <v>513.2639999999999</v>
+        <v>545.343</v>
       </c>
       <c r="G18">
         <v>151.8</v>
@@ -2763,45 +2763,45 @@
         <v>171.2</v>
       </c>
       <c r="M18">
-        <v>27.8702352</v>
+        <v>30.1574679</v>
       </c>
       <c r="N18">
-        <v>143.3297648</v>
+        <v>141.0425321</v>
       </c>
       <c r="O18">
-        <v>35.8324412</v>
+        <v>35.260633025</v>
       </c>
       <c r="P18">
-        <v>107.4973236</v>
+        <v>105.781899075</v>
       </c>
       <c r="Q18">
-        <v>343.1973236</v>
+        <v>341.481899075</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09433638267012158</v>
+        <v>0.0947932386817003</v>
       </c>
       <c r="T18">
-        <v>0.946064438962226</v>
+        <v>0.9549694129735423</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.142754044644733</v>
+        <v>5.676869177733585</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08572913810581123</v>
+        <v>0.08557971476872034</v>
       </c>
       <c r="C19">
-        <v>2375.158446766589</v>
+        <v>2353.479436107627</v>
       </c>
       <c r="D19">
-        <v>2768.701446766589</v>
+        <v>2779.101436107627</v>
       </c>
       <c r="E19">
-        <v>-994.457</v>
+        <v>-962.3779999999999</v>
       </c>
       <c r="F19">
-        <v>545.343</v>
+        <v>577.422</v>
       </c>
       <c r="G19">
         <v>151.8</v>
@@ -2845,28 +2845,28 @@
         <v>171.2</v>
       </c>
       <c r="M19">
-        <v>30.1574679</v>
+        <v>31.9314366</v>
       </c>
       <c r="N19">
-        <v>141.0425321</v>
+        <v>139.2685634</v>
       </c>
       <c r="O19">
-        <v>35.260633025</v>
+        <v>34.81714084999999</v>
       </c>
       <c r="P19">
-        <v>105.781899075</v>
+        <v>104.45142255</v>
       </c>
       <c r="Q19">
-        <v>341.481899075</v>
+        <v>340.15142255</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0947932386817003</v>
+        <v>0.09526123752282969</v>
       </c>
       <c r="T19">
-        <v>0.9549694129735423</v>
+        <v>0.9640915814729392</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.676869177733585</v>
+        <v>5.361487556748386</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08557971476872035</v>
+        <v>0.08543029143162947</v>
       </c>
       <c r="C20">
-        <v>2353.479436107626</v>
+        <v>2331.87885036339</v>
       </c>
       <c r="D20">
-        <v>2779.101436107626</v>
+        <v>2789.57985036339</v>
       </c>
       <c r="E20">
-        <v>-962.378</v>
+        <v>-930.299</v>
       </c>
       <c r="F20">
-        <v>577.4219999999999</v>
+        <v>609.501</v>
       </c>
       <c r="G20">
         <v>151.8</v>
@@ -2927,28 +2927,28 @@
         <v>171.2</v>
       </c>
       <c r="M20">
-        <v>31.9314366</v>
+        <v>33.7054053</v>
       </c>
       <c r="N20">
-        <v>139.2685634</v>
+        <v>137.4945947</v>
       </c>
       <c r="O20">
-        <v>34.81714085</v>
+        <v>34.373648675</v>
       </c>
       <c r="P20">
-        <v>104.45142255</v>
+        <v>103.120946025</v>
       </c>
       <c r="Q20">
-        <v>340.15142255</v>
+        <v>338.820946025</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09526123752282969</v>
+        <v>0.09574079189090057</v>
       </c>
       <c r="T20">
-        <v>0.9640915814729392</v>
+        <v>0.9734389887007165</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.361487556748386</v>
+        <v>5.079304001130049</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08543029143162947</v>
+        <v>0.08528086809453857</v>
       </c>
       <c r="C21">
-        <v>2331.87885036339</v>
+        <v>2310.357579978776</v>
       </c>
       <c r="D21">
-        <v>2789.57985036339</v>
+        <v>2800.137579978776</v>
       </c>
       <c r="E21">
-        <v>-930.299</v>
+        <v>-898.22</v>
       </c>
       <c r="F21">
-        <v>609.501</v>
+        <v>641.5799999999999</v>
       </c>
       <c r="G21">
         <v>151.8</v>
@@ -3009,28 +3009,28 @@
         <v>171.2</v>
       </c>
       <c r="M21">
-        <v>33.7054053</v>
+        <v>35.479374</v>
       </c>
       <c r="N21">
-        <v>137.4945947</v>
+        <v>135.720626</v>
       </c>
       <c r="O21">
-        <v>34.373648675</v>
+        <v>33.9301565</v>
       </c>
       <c r="P21">
-        <v>103.120946025</v>
+        <v>101.7904695</v>
       </c>
       <c r="Q21">
-        <v>338.820946025</v>
+        <v>337.4904695</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09574079189090057</v>
+        <v>0.09623233511817321</v>
       </c>
       <c r="T21">
-        <v>0.9734389887007165</v>
+        <v>0.983020081109188</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.079304001130049</v>
+        <v>4.825338801073547</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08528086809453857</v>
+        <v>0.08513144475744769</v>
       </c>
       <c r="C22">
-        <v>2310.357579978776</v>
+        <v>2288.916528930162</v>
       </c>
       <c r="D22">
-        <v>2800.137579978776</v>
+        <v>2810.775528930162</v>
       </c>
       <c r="E22">
-        <v>-898.22</v>
+        <v>-866.141</v>
       </c>
       <c r="F22">
-        <v>641.5799999999999</v>
+        <v>673.659</v>
       </c>
       <c r="G22">
         <v>151.8</v>
@@ -3091,28 +3091,28 @@
         <v>171.2</v>
       </c>
       <c r="M22">
-        <v>35.479374</v>
+        <v>37.2533427</v>
       </c>
       <c r="N22">
-        <v>135.720626</v>
+        <v>133.9466573</v>
       </c>
       <c r="O22">
-        <v>33.9301565</v>
+        <v>33.486664325</v>
       </c>
       <c r="P22">
-        <v>101.7904695</v>
+        <v>100.459992975</v>
       </c>
       <c r="Q22">
-        <v>337.4904695</v>
+        <v>336.159992975</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09623233511817321</v>
+        <v>0.09673632247778187</v>
       </c>
       <c r="T22">
-        <v>0.983020081109188</v>
+        <v>0.99284373281914</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.825338801073547</v>
+        <v>4.595560762927189</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08513144475744769</v>
+        <v>0.08539452142035678</v>
       </c>
       <c r="C23">
-        <v>2288.916528930163</v>
+        <v>2238.161979389177</v>
       </c>
       <c r="D23">
-        <v>2810.775528930162</v>
+        <v>2792.099979389177</v>
       </c>
       <c r="E23">
-        <v>-866.1410000000001</v>
+        <v>-834.062</v>
       </c>
       <c r="F23">
-        <v>673.6589999999999</v>
+        <v>705.7379999999999</v>
       </c>
       <c r="G23">
         <v>151.8</v>
@@ -3173,45 +3173,45 @@
         <v>171.2</v>
       </c>
       <c r="M23">
-        <v>37.2533427</v>
+        <v>40.7916564</v>
       </c>
       <c r="N23">
-        <v>133.9466573</v>
+        <v>130.4083436</v>
       </c>
       <c r="O23">
-        <v>33.486664325</v>
+        <v>32.6020859</v>
       </c>
       <c r="P23">
-        <v>100.459992975</v>
+        <v>97.8062577</v>
       </c>
       <c r="Q23">
-        <v>336.159992975</v>
+        <v>333.5062577</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09673632247778187</v>
+        <v>0.09725323259020099</v>
       </c>
       <c r="T23">
-        <v>0.99284373281914</v>
+        <v>1.002919273034475</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.595560762927189</v>
+        <v>4.196936704928707</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08539452142035678</v>
+        <v>0.0852638480832659</v>
       </c>
       <c r="C24">
-        <v>2238.161979389177</v>
+        <v>2215.328226356182</v>
       </c>
       <c r="D24">
-        <v>2792.099979389177</v>
+        <v>2801.345226356182</v>
       </c>
       <c r="E24">
-        <v>-834.062</v>
+        <v>-801.9830000000001</v>
       </c>
       <c r="F24">
-        <v>705.7379999999999</v>
+        <v>737.8169999999999</v>
       </c>
       <c r="G24">
         <v>151.8</v>
@@ -3255,28 +3255,28 @@
         <v>171.2</v>
       </c>
       <c r="M24">
-        <v>40.7916564</v>
+        <v>42.6458226</v>
       </c>
       <c r="N24">
-        <v>130.4083436</v>
+        <v>128.5541774</v>
       </c>
       <c r="O24">
-        <v>32.6020859</v>
+        <v>32.13854435</v>
       </c>
       <c r="P24">
-        <v>97.8062577</v>
+        <v>96.41563305</v>
       </c>
       <c r="Q24">
-        <v>333.5062577</v>
+        <v>332.11563305</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09725323259020099</v>
+        <v>0.09778356893930636</v>
       </c>
       <c r="T24">
-        <v>1.002919273034475</v>
+        <v>1.013256515593066</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.196936704928707</v>
+        <v>4.014461196018763</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0852638480832659</v>
+        <v>0.08576317474617501</v>
       </c>
       <c r="C25">
-        <v>2215.328226356182</v>
+        <v>2148.247343437291</v>
       </c>
       <c r="D25">
-        <v>2801.345226356182</v>
+        <v>2766.343343437291</v>
       </c>
       <c r="E25">
-        <v>-801.9830000000001</v>
+        <v>-769.904</v>
       </c>
       <c r="F25">
-        <v>737.8169999999999</v>
+        <v>769.896</v>
       </c>
       <c r="G25">
         <v>151.8</v>
@@ -3337,45 +3337,45 @@
         <v>171.2</v>
       </c>
       <c r="M25">
-        <v>42.6458226</v>
+        <v>47.1946248</v>
       </c>
       <c r="N25">
-        <v>128.5541774</v>
+        <v>124.0053752</v>
       </c>
       <c r="O25">
-        <v>32.13854435</v>
+        <v>31.0013438</v>
       </c>
       <c r="P25">
-        <v>96.41563305</v>
+        <v>93.00403139999999</v>
       </c>
       <c r="Q25">
-        <v>332.11563305</v>
+        <v>328.7040314</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09778356893930636</v>
+        <v>0.098327861508125</v>
       </c>
       <c r="T25">
-        <v>1.013256515593066</v>
+        <v>1.023865790850567</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.014461196018763</v>
+        <v>3.627531752302436</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08576317474617501</v>
+        <v>0.08618375140908413</v>
       </c>
       <c r="C26">
-        <v>2148.247343437291</v>
+        <v>2087.35825494259</v>
       </c>
       <c r="D26">
-        <v>2766.343343437291</v>
+        <v>2737.53325494259</v>
       </c>
       <c r="E26">
-        <v>-769.9040000000001</v>
+        <v>-737.825</v>
       </c>
       <c r="F26">
-        <v>769.8959999999998</v>
+        <v>801.9749999999999</v>
       </c>
       <c r="G26">
         <v>151.8</v>
@@ -3419,45 +3419,45 @@
         <v>171.2</v>
       </c>
       <c r="M26">
-        <v>47.19462479999999</v>
+        <v>51.4065975</v>
       </c>
       <c r="N26">
-        <v>124.0053752</v>
+        <v>119.7934025</v>
       </c>
       <c r="O26">
-        <v>31.0013438</v>
+        <v>29.948350625</v>
       </c>
       <c r="P26">
-        <v>93.0040314</v>
+        <v>89.845051875</v>
       </c>
       <c r="Q26">
-        <v>328.7040314</v>
+        <v>325.545051875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.098327861508125</v>
+        <v>0.09888666854544549</v>
       </c>
       <c r="T26">
-        <v>1.023865790850567</v>
+        <v>1.034757980114935</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.627531752302437</v>
+        <v>3.330311834001463</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08618375140908413</v>
+        <v>0.08610032807199322</v>
       </c>
       <c r="C27">
-        <v>2087.35825494259</v>
+        <v>2060.946061404232</v>
       </c>
       <c r="D27">
-        <v>2737.53325494259</v>
+        <v>2743.200061404232</v>
       </c>
       <c r="E27">
-        <v>-737.825</v>
+        <v>-705.746</v>
       </c>
       <c r="F27">
-        <v>801.9749999999999</v>
+        <v>834.054</v>
       </c>
       <c r="G27">
         <v>151.8</v>
@@ -3501,28 +3501,28 @@
         <v>171.2</v>
       </c>
       <c r="M27">
-        <v>51.4065975</v>
+        <v>53.4628614</v>
       </c>
       <c r="N27">
-        <v>119.7934025</v>
+        <v>117.7371386</v>
       </c>
       <c r="O27">
-        <v>29.948350625</v>
+        <v>29.43428465</v>
       </c>
       <c r="P27">
-        <v>89.845051875</v>
+        <v>88.30285394999999</v>
       </c>
       <c r="Q27">
-        <v>325.545051875</v>
+        <v>324.00285395</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09888666854544549</v>
+        <v>0.09946057847566651</v>
       </c>
       <c r="T27">
-        <v>1.034757980114935</v>
+        <v>1.045944552872934</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.330311834001463</v>
+        <v>3.202222917309098</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08610032807199322</v>
+        <v>0.08601690473490234</v>
       </c>
       <c r="C28">
-        <v>2060.946061404232</v>
+        <v>2034.557377576964</v>
       </c>
       <c r="D28">
-        <v>2743.200061404232</v>
+        <v>2748.890377576964</v>
       </c>
       <c r="E28">
-        <v>-705.746</v>
+        <v>-673.667</v>
       </c>
       <c r="F28">
-        <v>834.054</v>
+        <v>866.1329999999999</v>
       </c>
       <c r="G28">
         <v>151.8</v>
@@ -3583,28 +3583,28 @@
         <v>171.2</v>
       </c>
       <c r="M28">
-        <v>53.4628614</v>
+        <v>55.5191253</v>
       </c>
       <c r="N28">
-        <v>117.7371386</v>
+        <v>115.6808747</v>
       </c>
       <c r="O28">
-        <v>29.43428465</v>
+        <v>28.920218675</v>
       </c>
       <c r="P28">
-        <v>88.30285394999999</v>
+        <v>86.76065602499999</v>
       </c>
       <c r="Q28">
-        <v>324.00285395</v>
+        <v>322.460656025</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09946057847566651</v>
+        <v>0.1000502119656196</v>
       </c>
       <c r="T28">
-        <v>1.045944552872934</v>
+        <v>1.057437607076358</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.202222917309098</v>
+        <v>3.083622068519873</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08601690473490234</v>
+        <v>0.08757148139781144</v>
       </c>
       <c r="C29">
-        <v>2034.557377576964</v>
+        <v>1900.175067115477</v>
       </c>
       <c r="D29">
-        <v>2748.890377576964</v>
+        <v>2646.587067115477</v>
       </c>
       <c r="E29">
-        <v>-673.667</v>
+        <v>-641.588</v>
       </c>
       <c r="F29">
-        <v>866.1329999999999</v>
+        <v>898.212</v>
       </c>
       <c r="G29">
         <v>151.8</v>
@@ -3665,45 +3665,45 @@
         <v>171.2</v>
       </c>
       <c r="M29">
-        <v>55.5191253</v>
+        <v>64.5814428</v>
       </c>
       <c r="N29">
-        <v>115.6808747</v>
+        <v>106.6185572</v>
       </c>
       <c r="O29">
-        <v>28.920218675</v>
+        <v>26.6546393</v>
       </c>
       <c r="P29">
-        <v>86.76065602499999</v>
+        <v>79.96391789999998</v>
       </c>
       <c r="Q29">
-        <v>322.460656025</v>
+        <v>315.6639179</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1000502119656196</v>
+        <v>0.100656224163627</v>
       </c>
       <c r="T29">
-        <v>1.057437607076358</v>
+        <v>1.069249912785433</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.083622068519873</v>
+        <v>2.650916309351949</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08757148139781144</v>
+        <v>0.08754655806072055</v>
       </c>
       <c r="C30">
-        <v>1900.175067115477</v>
+        <v>1869.676120290595</v>
       </c>
       <c r="D30">
-        <v>2646.587067115477</v>
+        <v>2648.167120290595</v>
       </c>
       <c r="E30">
-        <v>-641.588</v>
+        <v>-609.5089999999999</v>
       </c>
       <c r="F30">
-        <v>898.212</v>
+        <v>930.2910000000001</v>
       </c>
       <c r="G30">
         <v>151.8</v>
@@ -3747,28 +3747,28 @@
         <v>171.2</v>
       </c>
       <c r="M30">
-        <v>64.5814428</v>
+        <v>66.88792290000001</v>
       </c>
       <c r="N30">
-        <v>106.6185572</v>
+        <v>104.3120771</v>
       </c>
       <c r="O30">
-        <v>26.6546393</v>
+        <v>26.078019275</v>
       </c>
       <c r="P30">
-        <v>79.96391789999998</v>
+        <v>78.23405782499998</v>
       </c>
       <c r="Q30">
-        <v>315.6639179</v>
+        <v>313.934057825</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.100656224163627</v>
+        <v>0.1012793071277754</v>
       </c>
       <c r="T30">
-        <v>1.069249912785433</v>
+        <v>1.081394959500397</v>
       </c>
       <c r="U30">
         <v>0.07190000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.650916309351949</v>
+        <v>2.559505402132916</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08754655806072054</v>
+        <v>0.08839913472362966</v>
       </c>
       <c r="C31">
-        <v>1869.676120290597</v>
+        <v>1784.596853949725</v>
       </c>
       <c r="D31">
-        <v>2648.167120290596</v>
+        <v>2595.166853949725</v>
       </c>
       <c r="E31">
-        <v>-609.5090000000001</v>
+        <v>-577.4300000000001</v>
       </c>
       <c r="F31">
-        <v>930.2909999999998</v>
+        <v>962.3699999999999</v>
       </c>
       <c r="G31">
         <v>151.8</v>
@@ -3829,45 +3829,45 @@
         <v>171.2</v>
       </c>
       <c r="M31">
-        <v>66.88792289999999</v>
+        <v>72.94764599999999</v>
       </c>
       <c r="N31">
-        <v>104.3120771</v>
+        <v>98.252354</v>
       </c>
       <c r="O31">
-        <v>26.078019275</v>
+        <v>24.5630885</v>
       </c>
       <c r="P31">
-        <v>78.23405782499999</v>
+        <v>73.6892655</v>
       </c>
       <c r="Q31">
-        <v>313.934057825</v>
+        <v>309.3892655</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1012793071277754</v>
+        <v>0.1019201924623281</v>
       </c>
       <c r="T31">
-        <v>1.081394959500397</v>
+        <v>1.093887007550074</v>
       </c>
       <c r="U31">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.559505402132916</v>
+        <v>2.346888616529175</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08839913472362966</v>
+        <v>0.08840346138653876</v>
       </c>
       <c r="C32">
-        <v>1784.596853949725</v>
+        <v>1752.254297614055</v>
       </c>
       <c r="D32">
-        <v>2595.166853949725</v>
+        <v>2594.903297614054</v>
       </c>
       <c r="E32">
-        <v>-577.4300000000001</v>
+        <v>-545.3510000000001</v>
       </c>
       <c r="F32">
-        <v>962.3699999999999</v>
+        <v>994.4489999999998</v>
       </c>
       <c r="G32">
         <v>151.8</v>
@@ -3911,28 +3911,28 @@
         <v>171.2</v>
       </c>
       <c r="M32">
-        <v>72.94764599999999</v>
+        <v>75.3792342</v>
       </c>
       <c r="N32">
-        <v>98.252354</v>
+        <v>95.82076579999999</v>
       </c>
       <c r="O32">
-        <v>24.5630885</v>
+        <v>23.95519145</v>
       </c>
       <c r="P32">
-        <v>73.6892655</v>
+        <v>71.86557434999999</v>
       </c>
       <c r="Q32">
-        <v>309.3892655</v>
+        <v>307.56557435</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1019201924623281</v>
+        <v>0.1025796541833895</v>
       </c>
       <c r="T32">
-        <v>1.093887007550074</v>
+        <v>1.106741143949017</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.346888616529175</v>
+        <v>2.271182532125008</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08840346138653876</v>
+        <v>0.08840778804944788</v>
       </c>
       <c r="C33">
-        <v>1752.254297614055</v>
+        <v>1719.911794804721</v>
       </c>
       <c r="D33">
-        <v>2594.903297614054</v>
+        <v>2594.639794804721</v>
       </c>
       <c r="E33">
-        <v>-545.3510000000001</v>
+        <v>-513.2720000000002</v>
       </c>
       <c r="F33">
-        <v>994.4489999999998</v>
+        <v>1026.528</v>
       </c>
       <c r="G33">
         <v>151.8</v>
@@ -3993,28 +3993,28 @@
         <v>171.2</v>
       </c>
       <c r="M33">
-        <v>75.3792342</v>
+        <v>77.81082239999999</v>
       </c>
       <c r="N33">
-        <v>95.82076579999999</v>
+        <v>93.3891776</v>
       </c>
       <c r="O33">
-        <v>23.95519145</v>
+        <v>23.3472944</v>
       </c>
       <c r="P33">
-        <v>71.86557434999999</v>
+        <v>70.0418832</v>
       </c>
       <c r="Q33">
-        <v>307.56557435</v>
+        <v>305.7418832</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1025796541833895</v>
+        <v>0.1032585118374234</v>
       </c>
       <c r="T33">
-        <v>1.106741143949017</v>
+        <v>1.119973343183224</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.271182532125008</v>
+        <v>2.200208077996102</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08840778804944788</v>
+        <v>0.08841211471235698</v>
       </c>
       <c r="C34">
-        <v>1719.911794804721</v>
+        <v>1687.569345505421</v>
       </c>
       <c r="D34">
-        <v>2594.639794804721</v>
+        <v>2594.376345505421</v>
       </c>
       <c r="E34">
-        <v>-513.2720000000002</v>
+        <v>-481.193</v>
       </c>
       <c r="F34">
-        <v>1026.528</v>
+        <v>1058.607</v>
       </c>
       <c r="G34">
         <v>151.8</v>
@@ -4075,28 +4075,28 @@
         <v>171.2</v>
       </c>
       <c r="M34">
-        <v>77.81082239999999</v>
+        <v>80.2424106</v>
       </c>
       <c r="N34">
-        <v>93.3891776</v>
+        <v>90.95758939999999</v>
       </c>
       <c r="O34">
-        <v>23.3472944</v>
+        <v>22.73939735</v>
       </c>
       <c r="P34">
-        <v>70.0418832</v>
+        <v>68.21819205</v>
       </c>
       <c r="Q34">
-        <v>305.7418832</v>
+        <v>303.91819205</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1032585118374234</v>
+        <v>0.1039576338990403</v>
       </c>
       <c r="T34">
-        <v>1.119973343183224</v>
+        <v>1.133600533439347</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.200208077996102</v>
+        <v>2.133535105935613</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08841211471235698</v>
+        <v>0.08841644137526609</v>
       </c>
       <c r="C35">
-        <v>1687.569345505421</v>
+        <v>1655.226949699855</v>
       </c>
       <c r="D35">
-        <v>2594.376345505421</v>
+        <v>2594.112949699855</v>
       </c>
       <c r="E35">
-        <v>-481.193</v>
+        <v>-449.114</v>
       </c>
       <c r="F35">
-        <v>1058.607</v>
+        <v>1090.686</v>
       </c>
       <c r="G35">
         <v>151.8</v>
@@ -4157,28 +4157,28 @@
         <v>171.2</v>
       </c>
       <c r="M35">
-        <v>80.2424106</v>
+        <v>82.67399880000001</v>
       </c>
       <c r="N35">
-        <v>90.95758939999999</v>
+        <v>88.52600119999998</v>
       </c>
       <c r="O35">
-        <v>22.73939735</v>
+        <v>22.1315003</v>
       </c>
       <c r="P35">
-        <v>68.21819205</v>
+        <v>66.39450089999998</v>
       </c>
       <c r="Q35">
-        <v>303.91819205</v>
+        <v>302.0945009</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1039576338990403</v>
+        <v>0.1046779414776759</v>
       </c>
       <c r="T35">
-        <v>1.133600533439347</v>
+        <v>1.147640668854746</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.133535105935613</v>
+        <v>2.070784073408095</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08841644137526609</v>
+        <v>0.0884207680381752</v>
       </c>
       <c r="C36">
-        <v>1655.226949699855</v>
+        <v>1622.884607371734</v>
       </c>
       <c r="D36">
-        <v>2594.112949699855</v>
+        <v>2593.849607371734</v>
       </c>
       <c r="E36">
-        <v>-449.114</v>
+        <v>-417.0350000000001</v>
       </c>
       <c r="F36">
-        <v>1090.686</v>
+        <v>1122.765</v>
       </c>
       <c r="G36">
         <v>151.8</v>
@@ -4239,28 +4239,28 @@
         <v>171.2</v>
       </c>
       <c r="M36">
-        <v>82.67399880000001</v>
+        <v>85.105587</v>
       </c>
       <c r="N36">
-        <v>88.52600119999998</v>
+        <v>86.09441299999999</v>
       </c>
       <c r="O36">
-        <v>22.1315003</v>
+        <v>21.52360325</v>
       </c>
       <c r="P36">
-        <v>66.39450089999998</v>
+        <v>64.57080975</v>
       </c>
       <c r="Q36">
-        <v>302.0945009</v>
+        <v>300.27080975</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1046779414776759</v>
+        <v>0.1054204123664234</v>
       </c>
       <c r="T36">
-        <v>1.147640668854746</v>
+        <v>1.162112808436773</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.070784073408095</v>
+        <v>2.011618814167864</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0884207680381752</v>
+        <v>0.0922590947010843</v>
       </c>
       <c r="C37">
-        <v>1622.884607371734</v>
+        <v>1376.508661389296</v>
       </c>
       <c r="D37">
-        <v>2593.849607371734</v>
+        <v>2379.552661389296</v>
       </c>
       <c r="E37">
-        <v>-417.0350000000001</v>
+        <v>-384.9559999999999</v>
       </c>
       <c r="F37">
-        <v>1122.765</v>
+        <v>1154.844</v>
       </c>
       <c r="G37">
         <v>151.8</v>
@@ -4321,45 +4321,45 @@
         <v>171.2</v>
       </c>
       <c r="M37">
-        <v>85.105587</v>
+        <v>103.93596</v>
       </c>
       <c r="N37">
-        <v>86.09441299999999</v>
+        <v>67.26403999999999</v>
       </c>
       <c r="O37">
-        <v>21.52360325</v>
+        <v>16.81601</v>
       </c>
       <c r="P37">
-        <v>64.57080975</v>
+        <v>50.44803</v>
       </c>
       <c r="Q37">
-        <v>300.27080975</v>
+        <v>286.14803</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1054204123664234</v>
+        <v>0.1061860854704442</v>
       </c>
       <c r="T37">
-        <v>1.162112808436773</v>
+        <v>1.177037202380738</v>
       </c>
       <c r="U37">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.011618814167864</v>
+        <v>1.647168121601032</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09225909470108432</v>
+        <v>0.09236992136399341</v>
       </c>
       <c r="C38">
-        <v>1376.508661389296</v>
+        <v>1338.766824241322</v>
       </c>
       <c r="D38">
-        <v>2379.552661389295</v>
+        <v>2373.889824241322</v>
       </c>
       <c r="E38">
-        <v>-384.9560000000001</v>
+        <v>-352.8770000000002</v>
       </c>
       <c r="F38">
-        <v>1154.844</v>
+        <v>1186.923</v>
       </c>
       <c r="G38">
         <v>151.8</v>
@@ -4403,28 +4403,28 @@
         <v>171.2</v>
       </c>
       <c r="M38">
-        <v>103.93596</v>
+        <v>106.82307</v>
       </c>
       <c r="N38">
-        <v>67.26404000000001</v>
+        <v>64.37693000000002</v>
       </c>
       <c r="O38">
-        <v>16.81601</v>
+        <v>16.0942325</v>
       </c>
       <c r="P38">
-        <v>50.44803</v>
+        <v>48.28269750000001</v>
       </c>
       <c r="Q38">
-        <v>286.14803</v>
+        <v>283.9826975</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1061860854704442</v>
+        <v>0.1069760656571324</v>
       </c>
       <c r="T38">
-        <v>1.177037202380738</v>
+        <v>1.192435386608639</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.647168121601032</v>
+        <v>1.602650064260464</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09236992136399341</v>
+        <v>0.09248074802690254</v>
       </c>
       <c r="C39">
-        <v>1338.766824241322</v>
+        <v>1301.051875837432</v>
       </c>
       <c r="D39">
-        <v>2373.889824241322</v>
+        <v>2368.253875837432</v>
       </c>
       <c r="E39">
-        <v>-352.8770000000002</v>
+        <v>-320.798</v>
       </c>
       <c r="F39">
-        <v>1186.923</v>
+        <v>1219.002</v>
       </c>
       <c r="G39">
         <v>151.8</v>
@@ -4485,28 +4485,28 @@
         <v>171.2</v>
       </c>
       <c r="M39">
-        <v>106.82307</v>
+        <v>109.71018</v>
       </c>
       <c r="N39">
-        <v>64.37693000000002</v>
+        <v>61.48981999999999</v>
       </c>
       <c r="O39">
-        <v>16.0942325</v>
+        <v>15.372455</v>
       </c>
       <c r="P39">
-        <v>48.28269750000001</v>
+        <v>46.11736499999999</v>
       </c>
       <c r="Q39">
-        <v>283.9826975</v>
+        <v>281.817365</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1069760656571324</v>
+        <v>0.1077915290756492</v>
       </c>
       <c r="T39">
-        <v>1.192435386608639</v>
+        <v>1.208330286456795</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.602650064260464</v>
+        <v>1.560475062569399</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09248074802690254</v>
+        <v>0.09259157468981165</v>
       </c>
       <c r="C40">
-        <v>1301.051875837432</v>
+        <v>1263.363625118247</v>
       </c>
       <c r="D40">
-        <v>2368.253875837432</v>
+        <v>2362.644625118246</v>
       </c>
       <c r="E40">
-        <v>-320.798</v>
+        <v>-288.7190000000001</v>
       </c>
       <c r="F40">
-        <v>1219.002</v>
+        <v>1251.081</v>
       </c>
       <c r="G40">
         <v>151.8</v>
@@ -4567,28 +4567,28 @@
         <v>171.2</v>
       </c>
       <c r="M40">
-        <v>109.71018</v>
+        <v>112.59729</v>
       </c>
       <c r="N40">
-        <v>61.48981999999999</v>
+        <v>58.60271</v>
       </c>
       <c r="O40">
-        <v>15.372455</v>
+        <v>14.6506775</v>
       </c>
       <c r="P40">
-        <v>46.11736499999999</v>
+        <v>43.9520325</v>
       </c>
       <c r="Q40">
-        <v>281.817365</v>
+        <v>279.6520325</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1077915290756492</v>
+        <v>0.1086337289996912</v>
       </c>
       <c r="T40">
-        <v>1.208330286456795</v>
+        <v>1.224746330562267</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.560475062569399</v>
+        <v>1.520462881477876</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09259157468981165</v>
+        <v>0.1114674059577015</v>
       </c>
       <c r="C41">
-        <v>1263.363625118247</v>
+        <v>552.1519467474081</v>
       </c>
       <c r="D41">
-        <v>2362.644625118246</v>
+        <v>1683.511946747408</v>
       </c>
       <c r="E41">
-        <v>-288.7190000000001</v>
+        <v>-256.6400000000001</v>
       </c>
       <c r="F41">
-        <v>1251.081</v>
+        <v>1283.16</v>
       </c>
       <c r="G41">
         <v>151.8</v>
@@ -4649,45 +4649,45 @@
         <v>171.2</v>
       </c>
       <c r="M41">
-        <v>112.59729</v>
+        <v>188.367888</v>
       </c>
       <c r="N41">
-        <v>58.60271</v>
+        <v>-17.167888</v>
       </c>
       <c r="O41">
-        <v>14.6506775</v>
+        <v>-4.291972000000001</v>
       </c>
       <c r="P41">
-        <v>43.9520325</v>
+        <v>-12.875916</v>
       </c>
       <c r="Q41">
-        <v>279.6520325</v>
+        <v>222.824084</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1086337289996912</v>
+        <v>0.1101491129044498</v>
       </c>
       <c r="T41">
-        <v>1.224746330562267</v>
+        <v>1.254283983448591</v>
       </c>
       <c r="U41">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.25</v>
+        <v>0.2272149486540933</v>
       </c>
       <c r="W41">
-        <v>0.0675</v>
+        <v>0.1134448455375791</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.520462881477876</v>
+        <v>0.9088597946163732</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1114674059577015</v>
+        <v>0.1124774059577016</v>
       </c>
       <c r="C42">
-        <v>552.1519467474081</v>
+        <v>494.5718487098873</v>
       </c>
       <c r="D42">
-        <v>1683.511946747408</v>
+        <v>1658.010848709887</v>
       </c>
       <c r="E42">
-        <v>-256.6400000000001</v>
+        <v>-224.5609999999999</v>
       </c>
       <c r="F42">
-        <v>1283.16</v>
+        <v>1315.239</v>
       </c>
       <c r="G42">
         <v>151.8</v>
@@ -4731,37 +4731,37 @@
         <v>171.2</v>
       </c>
       <c r="M42">
-        <v>188.367888</v>
+        <v>193.0770852</v>
       </c>
       <c r="N42">
-        <v>-17.167888</v>
+        <v>-21.87708520000004</v>
       </c>
       <c r="O42">
-        <v>-4.291972000000001</v>
+        <v>-5.46927130000001</v>
       </c>
       <c r="P42">
-        <v>-12.875916</v>
+        <v>-16.40781390000003</v>
       </c>
       <c r="Q42">
-        <v>222.824084</v>
+        <v>219.2921861</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1101491129044498</v>
+        <v>0.1112397758350337</v>
       </c>
       <c r="T42">
-        <v>1.254283983448591</v>
+        <v>1.275543034015517</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2272149486540933</v>
+        <v>0.2216731206381398</v>
       </c>
       <c r="W42">
-        <v>0.1134448455375791</v>
+        <v>0.1142583858903211</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.9088597946163732</v>
+        <v>0.8866924825525591</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1124774059577016</v>
+        <v>0.1134874059577015</v>
       </c>
       <c r="C43">
-        <v>494.5718487098873</v>
+        <v>437.7527817283956</v>
       </c>
       <c r="D43">
-        <v>1658.010848709887</v>
+        <v>1633.270781728396</v>
       </c>
       <c r="E43">
-        <v>-224.5609999999999</v>
+        <v>-192.482</v>
       </c>
       <c r="F43">
-        <v>1315.239</v>
+        <v>1347.318</v>
       </c>
       <c r="G43">
         <v>151.8</v>
@@ -4813,37 +4813,37 @@
         <v>171.2</v>
       </c>
       <c r="M43">
-        <v>193.0770852</v>
+        <v>197.7862824</v>
       </c>
       <c r="N43">
-        <v>-21.87708520000004</v>
+        <v>-26.58628240000002</v>
       </c>
       <c r="O43">
-        <v>-5.46927130000001</v>
+        <v>-6.646570600000004</v>
       </c>
       <c r="P43">
-        <v>-16.40781390000003</v>
+        <v>-19.93971180000001</v>
       </c>
       <c r="Q43">
-        <v>219.2921861</v>
+        <v>215.7602882</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1112397758350337</v>
+        <v>0.1123680478321895</v>
       </c>
       <c r="T43">
-        <v>1.275543034015517</v>
+        <v>1.297535155291646</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2216731206381398</v>
+        <v>0.2163951891943746</v>
       </c>
       <c r="W43">
-        <v>0.1142583858903211</v>
+        <v>0.1150331862262658</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8866924825525591</v>
+        <v>0.8655807567774982</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1134874059577016</v>
+        <v>0.1144974059577016</v>
       </c>
       <c r="C44">
-        <v>437.7527817283958</v>
+        <v>381.6611794103198</v>
       </c>
       <c r="D44">
-        <v>1633.270781728396</v>
+        <v>1609.25817941032</v>
       </c>
       <c r="E44">
-        <v>-192.4820000000002</v>
+        <v>-160.403</v>
       </c>
       <c r="F44">
-        <v>1347.318</v>
+        <v>1379.397</v>
       </c>
       <c r="G44">
         <v>151.8</v>
@@ -4895,37 +4895,37 @@
         <v>171.2</v>
       </c>
       <c r="M44">
-        <v>197.7862824</v>
+        <v>202.4954796</v>
       </c>
       <c r="N44">
-        <v>-26.58628239999999</v>
+        <v>-31.29547960000002</v>
       </c>
       <c r="O44">
-        <v>-6.646570599999997</v>
+        <v>-7.823869900000005</v>
       </c>
       <c r="P44">
-        <v>-19.93971179999999</v>
+        <v>-23.47160970000002</v>
       </c>
       <c r="Q44">
-        <v>215.7602882</v>
+        <v>212.2283903</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1123680478321895</v>
+        <v>0.1135359083204735</v>
       </c>
       <c r="T44">
-        <v>1.297535155291646</v>
+        <v>1.320298929945886</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.2163951891943746</v>
+        <v>0.2113627429340403</v>
       </c>
       <c r="W44">
-        <v>0.1150331862262658</v>
+        <v>0.1157719493372829</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8655807567774984</v>
+        <v>0.8454509717361611</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1144974059577016</v>
+        <v>0.1155074059577016</v>
       </c>
       <c r="C45">
-        <v>381.6611794103198</v>
+        <v>326.2654207549956</v>
       </c>
       <c r="D45">
-        <v>1609.25817941032</v>
+        <v>1585.941420754996</v>
       </c>
       <c r="E45">
-        <v>-160.403</v>
+        <v>-128.3240000000001</v>
       </c>
       <c r="F45">
-        <v>1379.397</v>
+        <v>1411.476</v>
       </c>
       <c r="G45">
         <v>151.8</v>
@@ -4977,37 +4977,37 @@
         <v>171.2</v>
       </c>
       <c r="M45">
-        <v>202.4954796</v>
+        <v>207.2046768</v>
       </c>
       <c r="N45">
-        <v>-31.29547960000002</v>
+        <v>-36.00467680000003</v>
       </c>
       <c r="O45">
-        <v>-7.823869900000005</v>
+        <v>-9.001169200000007</v>
       </c>
       <c r="P45">
-        <v>-23.47160970000002</v>
+        <v>-27.00350760000002</v>
       </c>
       <c r="Q45">
-        <v>212.2283903</v>
+        <v>208.6964924</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1135359083204735</v>
+        <v>0.1147454781119105</v>
       </c>
       <c r="T45">
-        <v>1.320298929945886</v>
+        <v>1.343875696552062</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2113627429340403</v>
+        <v>0.2065590442309939</v>
       </c>
       <c r="W45">
-        <v>0.1157719493372829</v>
+        <v>0.1164771323068901</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8454509717361611</v>
+        <v>0.8262361769239756</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1155074059577016</v>
+        <v>0.1165174059577015</v>
       </c>
       <c r="C46">
-        <v>326.2654207549956</v>
+        <v>271.5356912313391</v>
       </c>
       <c r="D46">
-        <v>1585.941420754996</v>
+        <v>1563.290691231339</v>
       </c>
       <c r="E46">
-        <v>-128.3240000000001</v>
+        <v>-96.24500000000012</v>
       </c>
       <c r="F46">
-        <v>1411.476</v>
+        <v>1443.555</v>
       </c>
       <c r="G46">
         <v>151.8</v>
@@ -5059,37 +5059,37 @@
         <v>171.2</v>
       </c>
       <c r="M46">
-        <v>207.2046768</v>
+        <v>211.913874</v>
       </c>
       <c r="N46">
-        <v>-36.00467680000003</v>
+        <v>-40.713874</v>
       </c>
       <c r="O46">
-        <v>-9.001169200000007</v>
+        <v>-10.1784685</v>
       </c>
       <c r="P46">
-        <v>-27.00350760000002</v>
+        <v>-30.5354055</v>
       </c>
       <c r="Q46">
-        <v>208.6964924</v>
+        <v>205.1645945</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1147454781119105</v>
+        <v>0.1159990322593998</v>
       </c>
       <c r="T46">
-        <v>1.343875696552062</v>
+        <v>1.368309800125736</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2065590442309939</v>
+        <v>0.201968843248083</v>
       </c>
       <c r="W46">
-        <v>0.1164771323068901</v>
+        <v>0.1171509738111814</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8262361769239756</v>
+        <v>0.8078753729923318</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1165174059577015</v>
+        <v>0.1434054180247288</v>
       </c>
       <c r="C47">
-        <v>271.5356912313391</v>
+        <v>-191.1933671440077</v>
       </c>
       <c r="D47">
-        <v>1563.290691231339</v>
+        <v>1132.640632855992</v>
       </c>
       <c r="E47">
-        <v>-96.24500000000012</v>
+        <v>-64.16600000000017</v>
       </c>
       <c r="F47">
-        <v>1443.555</v>
+        <v>1475.634</v>
       </c>
       <c r="G47">
         <v>151.8</v>
@@ -5141,45 +5141,45 @@
         <v>171.2</v>
       </c>
       <c r="M47">
-        <v>211.913874</v>
+        <v>296.3073072</v>
       </c>
       <c r="N47">
-        <v>-40.713874</v>
+        <v>-125.1073072</v>
       </c>
       <c r="O47">
-        <v>-10.1784685</v>
+        <v>-31.27682679999999</v>
       </c>
       <c r="P47">
-        <v>-30.5354055</v>
+        <v>-93.83048039999998</v>
       </c>
       <c r="Q47">
-        <v>205.1645945</v>
+        <v>141.8695196</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1159990322593998</v>
+        <v>0.1192212589068466</v>
       </c>
       <c r="T47">
-        <v>1.368309800125736</v>
+        <v>1.431116995011778</v>
       </c>
       <c r="U47">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.201968843248083</v>
+        <v>0.1444446321774679</v>
       </c>
       <c r="W47">
-        <v>0.1171509738111814</v>
+        <v>0.1717955178587644</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.8078753729923318</v>
+        <v>0.5777785287098718</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1434054180247288</v>
+        <v>0.1449554180247288</v>
       </c>
       <c r="C48">
-        <v>-191.1933671440077</v>
+        <v>-240.9778341361289</v>
       </c>
       <c r="D48">
-        <v>1132.640632855992</v>
+        <v>1114.935165863871</v>
       </c>
       <c r="E48">
-        <v>-64.16600000000017</v>
+        <v>-32.08699999999999</v>
       </c>
       <c r="F48">
-        <v>1475.634</v>
+        <v>1507.713</v>
       </c>
       <c r="G48">
         <v>151.8</v>
@@ -5223,37 +5223,37 @@
         <v>171.2</v>
       </c>
       <c r="M48">
-        <v>296.3073072</v>
+        <v>302.7487704</v>
       </c>
       <c r="N48">
-        <v>-125.1073072</v>
+        <v>-131.5487704</v>
       </c>
       <c r="O48">
-        <v>-31.27682679999999</v>
+        <v>-32.88719260000001</v>
       </c>
       <c r="P48">
-        <v>-93.83048039999998</v>
+        <v>-98.66157780000002</v>
       </c>
       <c r="Q48">
-        <v>141.8695196</v>
+        <v>137.0384222</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1192212589068466</v>
+        <v>0.1206065656786739</v>
       </c>
       <c r="T48">
-        <v>1.431116995011778</v>
+        <v>1.45811920246483</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1444446321774679</v>
+        <v>0.1413713421311388</v>
       </c>
       <c r="W48">
-        <v>0.1717955178587644</v>
+        <v>0.1724126345000673</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5777785287098718</v>
+        <v>0.5654853685245553</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1449554180247288</v>
+        <v>0.1465054180247288</v>
       </c>
       <c r="C49">
-        <v>-240.9778341361289</v>
+        <v>-290.2172763544875</v>
       </c>
       <c r="D49">
-        <v>1114.935165863871</v>
+        <v>1097.774723645512</v>
       </c>
       <c r="E49">
-        <v>-32.08699999999999</v>
+        <v>-0.008000000000038199</v>
       </c>
       <c r="F49">
-        <v>1507.713</v>
+        <v>1539.792</v>
       </c>
       <c r="G49">
         <v>151.8</v>
@@ -5305,37 +5305,37 @@
         <v>171.2</v>
       </c>
       <c r="M49">
-        <v>302.7487704</v>
+        <v>309.1902336</v>
       </c>
       <c r="N49">
-        <v>-131.5487704</v>
+        <v>-137.9902336</v>
       </c>
       <c r="O49">
-        <v>-32.88719260000001</v>
+        <v>-34.4975584</v>
       </c>
       <c r="P49">
-        <v>-98.66157780000002</v>
+        <v>-103.4926752</v>
       </c>
       <c r="Q49">
-        <v>137.0384222</v>
+        <v>132.2073248</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1206065656786739</v>
+        <v>0.1220451534801868</v>
       </c>
       <c r="T49">
-        <v>1.45811920246483</v>
+        <v>1.486159956358385</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1413713421311388</v>
+        <v>0.1384261058367401</v>
       </c>
       <c r="W49">
-        <v>0.1724126345000673</v>
+        <v>0.1730040379479826</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5654853685245553</v>
+        <v>0.5537044233469604</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1465054180247288</v>
+        <v>0.1480554180247288</v>
       </c>
       <c r="C50">
-        <v>-290.2172763544868</v>
+        <v>-338.9364784535003</v>
       </c>
       <c r="D50">
-        <v>1097.774723645513</v>
+        <v>1081.1345215465</v>
       </c>
       <c r="E50">
-        <v>-0.008000000000265572</v>
+        <v>32.07099999999991</v>
       </c>
       <c r="F50">
-        <v>1539.792</v>
+        <v>1571.871</v>
       </c>
       <c r="G50">
         <v>151.8</v>
@@ -5387,37 +5387,37 @@
         <v>171.2</v>
       </c>
       <c r="M50">
-        <v>309.1902335999999</v>
+        <v>315.6316968</v>
       </c>
       <c r="N50">
-        <v>-137.9902336</v>
+        <v>-144.4316968</v>
       </c>
       <c r="O50">
-        <v>-34.49755839999999</v>
+        <v>-36.1079242</v>
       </c>
       <c r="P50">
-        <v>-103.4926752</v>
+        <v>-108.3237726</v>
       </c>
       <c r="Q50">
-        <v>132.2073248</v>
+        <v>127.3762274</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1220451534801868</v>
+        <v>0.1235401564896023</v>
       </c>
       <c r="T50">
-        <v>1.486159956358385</v>
+        <v>1.51530034765953</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1384261058367401</v>
+        <v>0.1356010832686434</v>
       </c>
       <c r="W50">
-        <v>0.1730040379479826</v>
+        <v>0.1735713024796564</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5537044233469606</v>
+        <v>0.5424043330745736</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1480554180247288</v>
+        <v>0.1496054180247288</v>
       </c>
       <c r="C51">
-        <v>-338.9364784535003</v>
+        <v>-387.1587447712361</v>
       </c>
       <c r="D51">
-        <v>1081.1345215465</v>
+        <v>1064.991255228764</v>
       </c>
       <c r="E51">
-        <v>32.07099999999991</v>
+        <v>64.14999999999986</v>
       </c>
       <c r="F51">
-        <v>1571.871</v>
+        <v>1603.95</v>
       </c>
       <c r="G51">
         <v>151.8</v>
@@ -5469,37 +5469,37 @@
         <v>171.2</v>
       </c>
       <c r="M51">
-        <v>315.6316968</v>
+        <v>322.07316</v>
       </c>
       <c r="N51">
-        <v>-144.4316968</v>
+        <v>-150.87316</v>
       </c>
       <c r="O51">
-        <v>-36.1079242</v>
+        <v>-37.71829</v>
       </c>
       <c r="P51">
-        <v>-108.3237726</v>
+        <v>-113.15487</v>
       </c>
       <c r="Q51">
-        <v>127.3762274</v>
+        <v>122.54513</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1235401564896023</v>
+        <v>0.1250949596193943</v>
       </c>
       <c r="T51">
-        <v>1.51530034765953</v>
+        <v>1.54560635461272</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1356010832686434</v>
+        <v>0.1328890616032705</v>
       </c>
       <c r="W51">
-        <v>0.1735713024796564</v>
+        <v>0.1741158764300633</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5424043330745736</v>
+        <v>0.5315562464130821</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1496054180247288</v>
+        <v>0.1511554180247288</v>
       </c>
       <c r="C52">
-        <v>-387.1587447712361</v>
+        <v>-434.9060082222636</v>
       </c>
       <c r="D52">
-        <v>1064.991255228764</v>
+        <v>1049.322991777736</v>
       </c>
       <c r="E52">
-        <v>64.14999999999986</v>
+        <v>96.22899999999981</v>
       </c>
       <c r="F52">
-        <v>1603.95</v>
+        <v>1636.029</v>
       </c>
       <c r="G52">
         <v>151.8</v>
@@ -5551,37 +5551,37 @@
         <v>171.2</v>
       </c>
       <c r="M52">
-        <v>322.07316</v>
+        <v>328.5146232</v>
       </c>
       <c r="N52">
-        <v>-150.87316</v>
+        <v>-157.3146232</v>
       </c>
       <c r="O52">
-        <v>-37.71829</v>
+        <v>-39.32865579999999</v>
       </c>
       <c r="P52">
-        <v>-113.15487</v>
+        <v>-117.9859674</v>
       </c>
       <c r="Q52">
-        <v>122.54513</v>
+        <v>117.7140326</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1250949596193943</v>
+        <v>0.1267132241014227</v>
       </c>
       <c r="T52">
-        <v>1.54560635461272</v>
+        <v>1.577149341441551</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1328890616032705</v>
+        <v>0.1302833937286966</v>
       </c>
       <c r="W52">
-        <v>0.1741158764300633</v>
+        <v>0.1746390945392777</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5315562464130821</v>
+        <v>0.5211335749147863</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1511554180247288</v>
+        <v>0.1527054180247288</v>
       </c>
       <c r="C53">
-        <v>-434.9060082222636</v>
+        <v>-482.198929717611</v>
       </c>
       <c r="D53">
-        <v>1049.322991777736</v>
+        <v>1034.109070282389</v>
       </c>
       <c r="E53">
-        <v>96.22899999999981</v>
+        <v>128.308</v>
       </c>
       <c r="F53">
-        <v>1636.029</v>
+        <v>1668.108</v>
       </c>
       <c r="G53">
         <v>151.8</v>
@@ -5633,37 +5633,37 @@
         <v>171.2</v>
       </c>
       <c r="M53">
-        <v>328.5146232</v>
+        <v>334.9560864</v>
       </c>
       <c r="N53">
-        <v>-157.3146232</v>
+        <v>-163.7560864</v>
       </c>
       <c r="O53">
-        <v>-39.32865579999999</v>
+        <v>-40.9390216</v>
       </c>
       <c r="P53">
-        <v>-117.9859674</v>
+        <v>-122.8170648</v>
       </c>
       <c r="Q53">
-        <v>117.7140326</v>
+        <v>112.8829352</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1267132241014227</v>
+        <v>0.1283989162702024</v>
       </c>
       <c r="T53">
-        <v>1.577149341441551</v>
+        <v>1.61000661938825</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1302833937286966</v>
+        <v>0.1277779438492986</v>
       </c>
       <c r="W53">
-        <v>0.1746390945392777</v>
+        <v>0.1751421888750609</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5211335749147863</v>
+        <v>0.5111117753971942</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1527054180247288</v>
+        <v>0.1542554180247288</v>
       </c>
       <c r="C54">
-        <v>-482.198929717611</v>
+        <v>-529.0569890595077</v>
       </c>
       <c r="D54">
-        <v>1034.109070282389</v>
+        <v>1019.330010940492</v>
       </c>
       <c r="E54">
-        <v>128.308</v>
+        <v>160.3869999999999</v>
       </c>
       <c r="F54">
-        <v>1668.108</v>
+        <v>1700.187</v>
       </c>
       <c r="G54">
         <v>151.8</v>
@@ -5715,37 +5715,37 @@
         <v>171.2</v>
       </c>
       <c r="M54">
-        <v>334.9560864</v>
+        <v>341.3975496</v>
       </c>
       <c r="N54">
-        <v>-163.7560864</v>
+        <v>-170.1975496</v>
       </c>
       <c r="O54">
-        <v>-40.9390216</v>
+        <v>-42.5493874</v>
       </c>
       <c r="P54">
-        <v>-122.8170648</v>
+        <v>-127.6481622</v>
       </c>
       <c r="Q54">
-        <v>112.8829352</v>
+        <v>108.0518378</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1283989162702024</v>
+        <v>0.1301563400206322</v>
       </c>
       <c r="T54">
-        <v>1.61000661938825</v>
+        <v>1.644262079375234</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1277779438492986</v>
+        <v>0.1253670392483684</v>
       </c>
       <c r="W54">
-        <v>0.1751421888750609</v>
+        <v>0.1756262985189276</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5111117753971942</v>
+        <v>0.5014681569934736</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1542554180247288</v>
+        <v>0.1751242684315696</v>
       </c>
       <c r="C55">
-        <v>-529.0569890595077</v>
+        <v>-725.6236430126905</v>
       </c>
       <c r="D55">
-        <v>1019.330010940492</v>
+        <v>854.8423569873094</v>
       </c>
       <c r="E55">
-        <v>160.3869999999999</v>
+        <v>192.4659999999999</v>
       </c>
       <c r="F55">
-        <v>1700.187</v>
+        <v>1732.266</v>
       </c>
       <c r="G55">
         <v>151.8</v>
@@ -5797,45 +5797,45 @@
         <v>171.2</v>
       </c>
       <c r="M55">
-        <v>341.3975496</v>
+        <v>408.4683228</v>
       </c>
       <c r="N55">
-        <v>-170.1975496</v>
+        <v>-237.2683228</v>
       </c>
       <c r="O55">
-        <v>-42.5493874</v>
+        <v>-59.31708069999999</v>
       </c>
       <c r="P55">
-        <v>-127.6481622</v>
+        <v>-177.9512421</v>
       </c>
       <c r="Q55">
-        <v>108.0518378</v>
+        <v>57.74875790000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1301563400206322</v>
+        <v>0.1329007178620391</v>
       </c>
       <c r="T55">
-        <v>1.644262079375234</v>
+        <v>1.697755111612045</v>
       </c>
       <c r="U55">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1253670392483684</v>
+        <v>0.1047816871247476</v>
       </c>
       <c r="W55">
-        <v>0.1756262985189276</v>
+        <v>0.2110924781759845</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.5014681569934736</v>
+        <v>0.4191267484989903</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1751242684315696</v>
+        <v>0.1770242684315697</v>
       </c>
       <c r="C56">
-        <v>-725.6236430126905</v>
+        <v>-770.0799303673</v>
       </c>
       <c r="D56">
-        <v>854.8423569873094</v>
+        <v>842.4650696327</v>
       </c>
       <c r="E56">
-        <v>192.4659999999999</v>
+        <v>224.5450000000001</v>
       </c>
       <c r="F56">
-        <v>1732.266</v>
+        <v>1764.345</v>
       </c>
       <c r="G56">
         <v>151.8</v>
@@ -5879,37 +5879,37 @@
         <v>171.2</v>
       </c>
       <c r="M56">
-        <v>408.4683228</v>
+        <v>416.032551</v>
       </c>
       <c r="N56">
-        <v>-237.2683228</v>
+        <v>-244.832551</v>
       </c>
       <c r="O56">
-        <v>-59.31708069999999</v>
+        <v>-61.20813775000001</v>
       </c>
       <c r="P56">
-        <v>-177.9512421</v>
+        <v>-183.62441325</v>
       </c>
       <c r="Q56">
-        <v>57.74875790000002</v>
+        <v>52.07558674999996</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1329007178620391</v>
+        <v>0.1348362893700845</v>
       </c>
       <c r="T56">
-        <v>1.697755111612045</v>
+        <v>1.735483002981202</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1047816871247476</v>
+        <v>0.1028765655406613</v>
       </c>
       <c r="W56">
-        <v>0.2110924781759845</v>
+        <v>0.2115417058455121</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4191267484989903</v>
+        <v>0.411506262162645</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1770242684315697</v>
+        <v>0.1789242684315697</v>
       </c>
       <c r="C57">
-        <v>-770.0799303673</v>
+        <v>-814.1829110521207</v>
       </c>
       <c r="D57">
-        <v>842.4650696327</v>
+        <v>830.4410889478792</v>
       </c>
       <c r="E57">
-        <v>224.5450000000001</v>
+        <v>256.624</v>
       </c>
       <c r="F57">
-        <v>1764.345</v>
+        <v>1796.424</v>
       </c>
       <c r="G57">
         <v>151.8</v>
@@ -5961,37 +5961,37 @@
         <v>171.2</v>
       </c>
       <c r="M57">
-        <v>416.032551</v>
+        <v>423.5967792</v>
       </c>
       <c r="N57">
-        <v>-244.832551</v>
+        <v>-252.3967792</v>
       </c>
       <c r="O57">
-        <v>-61.20813775000001</v>
+        <v>-63.09919480000001</v>
       </c>
       <c r="P57">
-        <v>-183.62441325</v>
+        <v>-189.2975844</v>
       </c>
       <c r="Q57">
-        <v>52.07558674999996</v>
+        <v>46.40241559999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1348362893700845</v>
+        <v>0.1368598414012227</v>
       </c>
       <c r="T57">
-        <v>1.735483002981202</v>
+        <v>1.774925798503502</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1028765655406613</v>
+        <v>0.1010394840131495</v>
       </c>
       <c r="W57">
-        <v>0.2115417058455121</v>
+        <v>0.2119748896696994</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.411506262162645</v>
+        <v>0.4041579360525978</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1789242684315697</v>
+        <v>0.1808242684315697</v>
       </c>
       <c r="C58">
-        <v>-814.1829110521207</v>
+        <v>-857.9474997787179</v>
       </c>
       <c r="D58">
-        <v>830.4410889478792</v>
+        <v>818.755500221282</v>
       </c>
       <c r="E58">
-        <v>256.624</v>
+        <v>288.703</v>
       </c>
       <c r="F58">
-        <v>1796.424</v>
+        <v>1828.503</v>
       </c>
       <c r="G58">
         <v>151.8</v>
@@ -6043,37 +6043,37 @@
         <v>171.2</v>
       </c>
       <c r="M58">
-        <v>423.5967792</v>
+        <v>431.1610074</v>
       </c>
       <c r="N58">
-        <v>-252.3967792</v>
+        <v>-259.9610074</v>
       </c>
       <c r="O58">
-        <v>-63.09919480000001</v>
+        <v>-64.99025185000001</v>
       </c>
       <c r="P58">
-        <v>-189.2975844</v>
+        <v>-194.97075555</v>
       </c>
       <c r="Q58">
-        <v>46.40241559999998</v>
+        <v>40.72924444999995</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1368598414012227</v>
+        <v>0.1389775121314837</v>
       </c>
       <c r="T58">
-        <v>1.774925798503502</v>
+        <v>1.816203142654746</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1010394840131495</v>
+        <v>0.09926686148660296</v>
       </c>
       <c r="W58">
-        <v>0.2119748896696994</v>
+        <v>0.212392874061459</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4041579360525978</v>
+        <v>0.3970674459464119</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1808242684315697</v>
+        <v>0.1827242684315697</v>
       </c>
       <c r="C59">
-        <v>-857.9474997787179</v>
+        <v>-901.3877834155769</v>
       </c>
       <c r="D59">
-        <v>818.755500221282</v>
+        <v>807.3942165844231</v>
       </c>
       <c r="E59">
-        <v>288.703</v>
+        <v>320.7820000000002</v>
       </c>
       <c r="F59">
-        <v>1828.503</v>
+        <v>1860.582</v>
       </c>
       <c r="G59">
         <v>151.8</v>
@@ -6125,37 +6125,37 @@
         <v>171.2</v>
       </c>
       <c r="M59">
-        <v>431.1610074</v>
+        <v>438.7252356</v>
       </c>
       <c r="N59">
-        <v>-259.9610074</v>
+        <v>-267.5252356</v>
       </c>
       <c r="O59">
-        <v>-64.99025185000001</v>
+        <v>-66.88130890000001</v>
       </c>
       <c r="P59">
-        <v>-194.97075555</v>
+        <v>-200.6439267</v>
       </c>
       <c r="Q59">
-        <v>40.72924444999995</v>
+        <v>35.05607329999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1389775121314837</v>
+        <v>0.1411960243250905</v>
       </c>
       <c r="T59">
-        <v>1.816203142654746</v>
+        <v>1.859446074622716</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09926686148660296</v>
+        <v>0.09755536387476497</v>
       </c>
       <c r="W59">
-        <v>0.212392874061459</v>
+        <v>0.2127964451983304</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3970674459464119</v>
+        <v>0.39022145549906</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1827242684315696</v>
+        <v>0.1846242684315696</v>
       </c>
       <c r="C60">
-        <v>-901.3877834155762</v>
+        <v>-944.5170776389277</v>
       </c>
       <c r="D60">
-        <v>807.3942165844235</v>
+        <v>796.3439223610718</v>
       </c>
       <c r="E60">
-        <v>320.7819999999997</v>
+        <v>352.8609999999996</v>
       </c>
       <c r="F60">
-        <v>1860.582</v>
+        <v>1892.661</v>
       </c>
       <c r="G60">
         <v>151.8</v>
@@ -6207,37 +6207,37 @@
         <v>171.2</v>
       </c>
       <c r="M60">
-        <v>438.7252356</v>
+        <v>446.2894637999999</v>
       </c>
       <c r="N60">
-        <v>-267.5252356</v>
+        <v>-275.0894637999999</v>
       </c>
       <c r="O60">
-        <v>-66.88130889999999</v>
+        <v>-68.77236594999998</v>
       </c>
       <c r="P60">
-        <v>-200.6439267</v>
+        <v>-206.3170978499999</v>
       </c>
       <c r="Q60">
-        <v>35.05607330000001</v>
+        <v>29.38290215000006</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1411960243250905</v>
+        <v>0.1435227566257024</v>
       </c>
       <c r="T60">
-        <v>1.859446074622716</v>
+        <v>1.904798417906196</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.09755536387476499</v>
+        <v>0.09590188313112492</v>
       </c>
       <c r="W60">
-        <v>0.2127964451983304</v>
+        <v>0.2131863359576807</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.39022145549906</v>
+        <v>0.3836075325244996</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1846242684315696</v>
+        <v>0.1865242684315696</v>
       </c>
       <c r="C61">
-        <v>-944.5170776389277</v>
+        <v>-987.3479789943208</v>
       </c>
       <c r="D61">
-        <v>796.3439223610718</v>
+        <v>785.592021005679</v>
       </c>
       <c r="E61">
-        <v>352.8609999999996</v>
+        <v>384.9399999999998</v>
       </c>
       <c r="F61">
-        <v>1892.661</v>
+        <v>1924.74</v>
       </c>
       <c r="G61">
         <v>151.8</v>
@@ -6289,37 +6289,37 @@
         <v>171.2</v>
       </c>
       <c r="M61">
-        <v>446.2894637999999</v>
+        <v>453.853692</v>
       </c>
       <c r="N61">
-        <v>-275.0894637999999</v>
+        <v>-282.653692</v>
       </c>
       <c r="O61">
-        <v>-68.77236594999998</v>
+        <v>-70.66342299999999</v>
       </c>
       <c r="P61">
-        <v>-206.3170978499999</v>
+        <v>-211.990269</v>
       </c>
       <c r="Q61">
-        <v>29.38290215000006</v>
+        <v>23.709731</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1435227566257024</v>
+        <v>0.145965825541345</v>
       </c>
       <c r="T61">
-        <v>1.904798417906196</v>
+        <v>1.952418378353851</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.09590188313112492</v>
+        <v>0.09430351841227283</v>
       </c>
       <c r="W61">
-        <v>0.2131863359576807</v>
+        <v>0.2135632303583861</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3836075325244996</v>
+        <v>0.3772140736490913</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1865242684315696</v>
+        <v>0.1884242684315696</v>
       </c>
       <c r="C62">
-        <v>-987.3479789943208</v>
+        <v>-1029.892412796892</v>
       </c>
       <c r="D62">
-        <v>785.592021005679</v>
+        <v>775.1265872031074</v>
       </c>
       <c r="E62">
-        <v>384.9399999999998</v>
+        <v>417.0189999999998</v>
       </c>
       <c r="F62">
-        <v>1924.74</v>
+        <v>1956.819</v>
       </c>
       <c r="G62">
         <v>151.8</v>
@@ -6371,37 +6371,37 @@
         <v>171.2</v>
       </c>
       <c r="M62">
-        <v>453.853692</v>
+        <v>461.4179202</v>
       </c>
       <c r="N62">
-        <v>-282.653692</v>
+        <v>-290.2179202</v>
       </c>
       <c r="O62">
-        <v>-70.66342299999999</v>
+        <v>-72.55448005</v>
       </c>
       <c r="P62">
-        <v>-211.990269</v>
+        <v>-217.66344015</v>
       </c>
       <c r="Q62">
-        <v>23.709731</v>
+        <v>18.03655985</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.145965825541345</v>
+        <v>0.1485341800424051</v>
       </c>
       <c r="T62">
-        <v>1.952418378353851</v>
+        <v>2.002480388055232</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.09430351841227283</v>
+        <v>0.09275755909403885</v>
       </c>
       <c r="W62">
-        <v>0.2135632303583861</v>
+        <v>0.2139277675656256</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3772140736490913</v>
+        <v>0.3710302363761554</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1884242684315696</v>
+        <v>0.1903242684315696</v>
       </c>
       <c r="C63">
-        <v>-1029.892412796892</v>
+        <v>-1072.161677253296</v>
       </c>
       <c r="D63">
-        <v>775.1265872031074</v>
+        <v>764.936322746704</v>
       </c>
       <c r="E63">
-        <v>417.0189999999998</v>
+        <v>449.0979999999997</v>
       </c>
       <c r="F63">
-        <v>1956.819</v>
+        <v>1988.898</v>
       </c>
       <c r="G63">
         <v>151.8</v>
@@ -6453,37 +6453,37 @@
         <v>171.2</v>
       </c>
       <c r="M63">
-        <v>461.4179202</v>
+        <v>468.9821484</v>
       </c>
       <c r="N63">
-        <v>-290.2179202</v>
+        <v>-297.7821484</v>
       </c>
       <c r="O63">
-        <v>-72.55448005</v>
+        <v>-74.4455371</v>
       </c>
       <c r="P63">
-        <v>-217.66344015</v>
+        <v>-223.3366113</v>
       </c>
       <c r="Q63">
-        <v>18.03655985</v>
+        <v>12.3633887</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1485341800424051</v>
+        <v>0.1512377110961526</v>
       </c>
       <c r="T63">
-        <v>2.002480388055232</v>
+        <v>2.055177240372475</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09275755909403885</v>
+        <v>0.09126146943123177</v>
       </c>
       <c r="W63">
-        <v>0.2139277675656256</v>
+        <v>0.2142805455081155</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3710302363761554</v>
+        <v>0.365045877724927</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1903242684315696</v>
+        <v>0.1922242684315696</v>
       </c>
       <c r="C64">
-        <v>-1072.161677253296</v>
+        <v>-1114.166484148469</v>
       </c>
       <c r="D64">
-        <v>764.936322746704</v>
+        <v>755.010515851531</v>
       </c>
       <c r="E64">
-        <v>449.0979999999997</v>
+        <v>481.1769999999999</v>
       </c>
       <c r="F64">
-        <v>1988.898</v>
+        <v>2020.977</v>
       </c>
       <c r="G64">
         <v>151.8</v>
@@ -6535,37 +6535,37 @@
         <v>171.2</v>
       </c>
       <c r="M64">
-        <v>468.9821484</v>
+        <v>476.5463766</v>
       </c>
       <c r="N64">
-        <v>-297.7821484</v>
+        <v>-305.3463766</v>
       </c>
       <c r="O64">
-        <v>-74.4455371</v>
+        <v>-76.33659415</v>
       </c>
       <c r="P64">
-        <v>-223.3366113</v>
+        <v>-229.00978245</v>
       </c>
       <c r="Q64">
-        <v>12.3633887</v>
+        <v>6.69021755</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1512377110961526</v>
+        <v>0.1540873789636162</v>
       </c>
       <c r="T64">
-        <v>2.055177240372475</v>
+        <v>2.110722571193353</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.09126146943123177</v>
+        <v>0.08981287467835507</v>
       </c>
       <c r="W64">
-        <v>0.2142805455081155</v>
+        <v>0.2146221241508439</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.365045877724927</v>
+        <v>0.3592514987134203</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1922242684315696</v>
+        <v>0.1941242684315697</v>
       </c>
       <c r="C65">
-        <v>-1114.166484148469</v>
+        <v>-1155.916996405276</v>
       </c>
       <c r="D65">
-        <v>755.010515851531</v>
+        <v>745.3390035947236</v>
       </c>
       <c r="E65">
-        <v>481.1769999999999</v>
+        <v>513.2559999999996</v>
       </c>
       <c r="F65">
-        <v>2020.977</v>
+        <v>2053.056</v>
       </c>
       <c r="G65">
         <v>151.8</v>
@@ -6617,37 +6617,37 @@
         <v>171.2</v>
       </c>
       <c r="M65">
-        <v>476.5463766</v>
+        <v>484.1106047999999</v>
       </c>
       <c r="N65">
-        <v>-305.3463766</v>
+        <v>-312.9106047999999</v>
       </c>
       <c r="O65">
-        <v>-76.33659415</v>
+        <v>-78.22765119999998</v>
       </c>
       <c r="P65">
-        <v>-229.00978245</v>
+        <v>-234.6829536</v>
       </c>
       <c r="Q65">
-        <v>6.69021755</v>
+        <v>1.017046400000027</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1540873789636162</v>
+        <v>0.1570953617126056</v>
       </c>
       <c r="T65">
-        <v>2.110722571193353</v>
+        <v>2.169353753726502</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08981287467835507</v>
+        <v>0.08840954851150579</v>
       </c>
       <c r="W65">
-        <v>0.2146221241508439</v>
+        <v>0.214953028460987</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3592514987134203</v>
+        <v>0.3536381940460231</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1941242684315697</v>
+        <v>0.1960242684315696</v>
       </c>
       <c r="C66">
-        <v>-1155.916996405276</v>
+        <v>-1197.422862793879</v>
       </c>
       <c r="D66">
-        <v>745.3390035947236</v>
+        <v>735.9121372061211</v>
       </c>
       <c r="E66">
-        <v>513.2559999999996</v>
+        <v>545.3349999999998</v>
       </c>
       <c r="F66">
-        <v>2053.056</v>
+        <v>2085.135</v>
       </c>
       <c r="G66">
         <v>151.8</v>
@@ -6699,37 +6699,37 @@
         <v>171.2</v>
       </c>
       <c r="M66">
-        <v>484.1106047999999</v>
+        <v>491.674833</v>
       </c>
       <c r="N66">
-        <v>-312.9106047999999</v>
+        <v>-320.474833</v>
       </c>
       <c r="O66">
-        <v>-78.22765119999998</v>
+        <v>-80.11870825</v>
       </c>
       <c r="P66">
-        <v>-234.6829536</v>
+        <v>-240.35612475</v>
       </c>
       <c r="Q66">
-        <v>1.017046400000027</v>
+        <v>-4.656124750000004</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1570953617126056</v>
+        <v>0.1602752291901086</v>
       </c>
       <c r="T66">
-        <v>2.169353753726502</v>
+        <v>2.231335289547259</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08840954851150579</v>
+        <v>0.08704940161132876</v>
       </c>
       <c r="W66">
-        <v>0.214953028460987</v>
+        <v>0.2152737511000487</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3536381940460231</v>
+        <v>0.3481976064453151</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1960242684315696</v>
+        <v>0.1979242684315696</v>
       </c>
       <c r="C67">
-        <v>-1197.422862793879</v>
+        <v>-1238.693250040027</v>
       </c>
       <c r="D67">
-        <v>735.9121372061211</v>
+        <v>726.7207499599725</v>
       </c>
       <c r="E67">
-        <v>545.3349999999998</v>
+        <v>577.414</v>
       </c>
       <c r="F67">
-        <v>2085.135</v>
+        <v>2117.214</v>
       </c>
       <c r="G67">
         <v>151.8</v>
@@ -6781,37 +6781,37 @@
         <v>171.2</v>
       </c>
       <c r="M67">
-        <v>491.674833</v>
+        <v>499.2390612</v>
       </c>
       <c r="N67">
-        <v>-320.474833</v>
+        <v>-328.0390612</v>
       </c>
       <c r="O67">
-        <v>-80.11870825</v>
+        <v>-82.0097653</v>
       </c>
       <c r="P67">
-        <v>-240.35612475</v>
+        <v>-246.0292959</v>
       </c>
       <c r="Q67">
-        <v>-4.656124750000004</v>
+        <v>-10.32929590000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1602752291901086</v>
+        <v>0.1636421476957</v>
       </c>
       <c r="T67">
-        <v>2.231335289547259</v>
+        <v>2.296962798063355</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08704940161132876</v>
+        <v>0.08573047128388439</v>
       </c>
       <c r="W67">
-        <v>0.2152737511000487</v>
+        <v>0.2155847548712601</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3481976064453151</v>
+        <v>0.3429218851355376</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1979242684315696</v>
+        <v>0.1998242684315696</v>
       </c>
       <c r="C68">
-        <v>-1238.693250040027</v>
+        <v>-1279.736872556883</v>
       </c>
       <c r="D68">
-        <v>726.7207499599725</v>
+        <v>717.7561274431165</v>
       </c>
       <c r="E68">
-        <v>577.414</v>
+        <v>609.4929999999997</v>
       </c>
       <c r="F68">
-        <v>2117.214</v>
+        <v>2149.293</v>
       </c>
       <c r="G68">
         <v>151.8</v>
@@ -6863,37 +6863,37 @@
         <v>171.2</v>
       </c>
       <c r="M68">
-        <v>499.2390612</v>
+        <v>506.8032893999999</v>
       </c>
       <c r="N68">
-        <v>-328.0390612</v>
+        <v>-335.6032893999999</v>
       </c>
       <c r="O68">
-        <v>-82.0097653</v>
+        <v>-83.90082234999998</v>
       </c>
       <c r="P68">
-        <v>-246.0292959</v>
+        <v>-251.7024670499999</v>
       </c>
       <c r="Q68">
-        <v>-10.32929590000001</v>
+        <v>-16.00246704999995</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1636421476957</v>
+        <v>0.167213121868297</v>
       </c>
       <c r="T68">
-        <v>2.296962798063355</v>
+        <v>2.366567731338002</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08573047128388439</v>
+        <v>0.0844509120109906</v>
       </c>
       <c r="W68">
-        <v>0.2155847548712601</v>
+        <v>0.2158864749478084</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3429218851355376</v>
+        <v>0.3378036480439623</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1998242684315696</v>
+        <v>0.2017242684315697</v>
       </c>
       <c r="C69">
-        <v>-1279.736872556883</v>
+        <v>-1320.562020003074</v>
       </c>
       <c r="D69">
-        <v>717.7561274431165</v>
+        <v>709.0099799969255</v>
       </c>
       <c r="E69">
-        <v>609.4929999999997</v>
+        <v>641.5719999999999</v>
       </c>
       <c r="F69">
-        <v>2149.293</v>
+        <v>2181.372</v>
       </c>
       <c r="G69">
         <v>151.8</v>
@@ -6945,37 +6945,37 @@
         <v>171.2</v>
       </c>
       <c r="M69">
-        <v>506.8032893999999</v>
+        <v>514.3675175999999</v>
       </c>
       <c r="N69">
-        <v>-335.6032893999999</v>
+        <v>-343.1675175999999</v>
       </c>
       <c r="O69">
-        <v>-83.90082234999998</v>
+        <v>-85.79187939999998</v>
       </c>
       <c r="P69">
-        <v>-251.7024670499999</v>
+        <v>-257.3756382</v>
       </c>
       <c r="Q69">
-        <v>-16.00246704999995</v>
+        <v>-21.67563819999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.167213121868297</v>
+        <v>0.1710072819266813</v>
       </c>
       <c r="T69">
-        <v>2.366567731338002</v>
+        <v>2.440522972942315</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0844509120109906</v>
+        <v>0.08320898683435839</v>
       </c>
       <c r="W69">
-        <v>0.2158864749478084</v>
+        <v>0.2161793209044583</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3378036480439623</v>
+        <v>0.3328359473374335</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2017242684315697</v>
+        <v>0.2036242684315697</v>
       </c>
       <c r="C70">
-        <v>-1320.562020003074</v>
+        <v>-1361.176582850168</v>
       </c>
       <c r="D70">
-        <v>709.0099799969255</v>
+        <v>700.4744171498324</v>
       </c>
       <c r="E70">
-        <v>641.5719999999999</v>
+        <v>673.6510000000001</v>
       </c>
       <c r="F70">
-        <v>2181.372</v>
+        <v>2213.451</v>
       </c>
       <c r="G70">
         <v>151.8</v>
@@ -7027,37 +7027,37 @@
         <v>171.2</v>
       </c>
       <c r="M70">
-        <v>514.3675175999999</v>
+        <v>521.9317458</v>
       </c>
       <c r="N70">
-        <v>-343.1675175999999</v>
+        <v>-350.7317458000001</v>
       </c>
       <c r="O70">
-        <v>-85.79187939999998</v>
+        <v>-87.68293645000001</v>
       </c>
       <c r="P70">
-        <v>-257.3756382</v>
+        <v>-263.0488093500001</v>
       </c>
       <c r="Q70">
-        <v>-21.67563819999998</v>
+        <v>-27.34880935000007</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1710072819266813</v>
+        <v>0.1750462265049613</v>
       </c>
       <c r="T70">
-        <v>2.440522972942315</v>
+        <v>2.519249520456583</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08320898683435839</v>
+        <v>0.08200305948893288</v>
       </c>
       <c r="W70">
-        <v>0.2161793209044583</v>
+        <v>0.2164636785725096</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3328359473374335</v>
+        <v>0.3280122379557315</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2036242684315697</v>
+        <v>0.2055242684315697</v>
       </c>
       <c r="C71">
-        <v>-1361.176582850168</v>
+        <v>-1401.58807612532</v>
       </c>
       <c r="D71">
-        <v>700.4744171498324</v>
+        <v>692.1419238746798</v>
       </c>
       <c r="E71">
-        <v>673.6510000000001</v>
+        <v>705.7299999999998</v>
       </c>
       <c r="F71">
-        <v>2213.451</v>
+        <v>2245.53</v>
       </c>
       <c r="G71">
         <v>151.8</v>
@@ -7109,37 +7109,37 @@
         <v>171.2</v>
       </c>
       <c r="M71">
-        <v>521.9317458</v>
+        <v>529.4959739999999</v>
       </c>
       <c r="N71">
-        <v>-350.7317458000001</v>
+        <v>-358.2959739999999</v>
       </c>
       <c r="O71">
-        <v>-87.68293645000001</v>
+        <v>-89.57399349999999</v>
       </c>
       <c r="P71">
-        <v>-263.0488093500001</v>
+        <v>-268.7219805</v>
       </c>
       <c r="Q71">
-        <v>-27.34880935000007</v>
+        <v>-33.02198049999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1750462265049613</v>
+        <v>0.1793544340551267</v>
       </c>
       <c r="T71">
-        <v>2.519249520456583</v>
+        <v>2.603224504471803</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08200305948893288</v>
+        <v>0.08083158721051957</v>
       </c>
       <c r="W71">
-        <v>0.2164636785725096</v>
+        <v>0.2167399117357595</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3280122379557315</v>
+        <v>0.3233263488420782</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2055242684315697</v>
+        <v>0.2074242684315697</v>
       </c>
       <c r="C72">
-        <v>-1401.58807612532</v>
+        <v>-1441.803661479262</v>
       </c>
       <c r="D72">
-        <v>692.1419238746798</v>
+        <v>684.0053385207381</v>
       </c>
       <c r="E72">
-        <v>705.7299999999998</v>
+        <v>737.809</v>
       </c>
       <c r="F72">
-        <v>2245.53</v>
+        <v>2277.609</v>
       </c>
       <c r="G72">
         <v>151.8</v>
@@ -7191,37 +7191,37 @@
         <v>171.2</v>
       </c>
       <c r="M72">
-        <v>529.4959739999999</v>
+        <v>537.0602022</v>
       </c>
       <c r="N72">
-        <v>-358.2959739999999</v>
+        <v>-365.8602022000001</v>
       </c>
       <c r="O72">
-        <v>-89.57399349999999</v>
+        <v>-91.46505055000002</v>
       </c>
       <c r="P72">
-        <v>-268.7219805</v>
+        <v>-274.3951516500001</v>
       </c>
       <c r="Q72">
-        <v>-33.02198049999998</v>
+        <v>-38.69515165000007</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1793544340551267</v>
+        <v>0.1839597593673725</v>
       </c>
       <c r="T72">
-        <v>2.603224504471803</v>
+        <v>2.692990866694969</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08083158721051957</v>
+        <v>0.07969311415121647</v>
       </c>
       <c r="W72">
-        <v>0.2167399117357595</v>
+        <v>0.2170083636831432</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3233263488420782</v>
+        <v>0.3187724566048659</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2074242684315696</v>
+        <v>0.2093242684315696</v>
       </c>
       <c r="C73">
-        <v>-1441.803661479261</v>
+        <v>-1481.830167715825</v>
       </c>
       <c r="D73">
-        <v>684.0053385207381</v>
+        <v>676.0578322841747</v>
       </c>
       <c r="E73">
-        <v>737.8089999999995</v>
+        <v>769.8879999999997</v>
       </c>
       <c r="F73">
-        <v>2277.608999999999</v>
+        <v>2309.688</v>
       </c>
       <c r="G73">
         <v>151.8</v>
@@ -7273,37 +7273,37 @@
         <v>171.2</v>
       </c>
       <c r="M73">
-        <v>537.0602021999999</v>
+        <v>544.6244303999999</v>
       </c>
       <c r="N73">
-        <v>-365.8602021999999</v>
+        <v>-373.4244303999999</v>
       </c>
       <c r="O73">
-        <v>-91.46505054999999</v>
+        <v>-93.35610759999999</v>
       </c>
       <c r="P73">
-        <v>-274.3951516499999</v>
+        <v>-280.0683228</v>
       </c>
       <c r="Q73">
-        <v>-38.69515164999996</v>
+        <v>-44.36832279999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1839597593673724</v>
+        <v>0.1888940364876357</v>
       </c>
       <c r="T73">
-        <v>2.692990866694967</v>
+        <v>2.789169111934073</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07969311415121648</v>
+        <v>0.0785862653435607</v>
       </c>
       <c r="W73">
-        <v>0.2170083636831432</v>
+        <v>0.2172693586319884</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3187724566048659</v>
+        <v>0.3143450613742428</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2093242684315696</v>
+        <v>0.2112242684315697</v>
       </c>
       <c r="C74">
-        <v>-1481.830167715825</v>
+        <v>-1521.674109906706</v>
       </c>
       <c r="D74">
-        <v>676.0578322841747</v>
+        <v>668.2928900932935</v>
       </c>
       <c r="E74">
-        <v>769.8879999999997</v>
+        <v>801.9669999999999</v>
       </c>
       <c r="F74">
-        <v>2309.688</v>
+        <v>2341.767</v>
       </c>
       <c r="G74">
         <v>151.8</v>
@@ -7355,37 +7355,37 @@
         <v>171.2</v>
       </c>
       <c r="M74">
-        <v>544.6244303999999</v>
+        <v>552.1886585999999</v>
       </c>
       <c r="N74">
-        <v>-373.4244303999999</v>
+        <v>-380.9886586</v>
       </c>
       <c r="O74">
-        <v>-93.35610759999999</v>
+        <v>-95.24716464999999</v>
       </c>
       <c r="P74">
-        <v>-280.0683228</v>
+        <v>-285.7414939499999</v>
       </c>
       <c r="Q74">
-        <v>-44.36832279999999</v>
+        <v>-50.04149394999996</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1888940364876357</v>
+        <v>0.1941938156168074</v>
       </c>
       <c r="T74">
-        <v>2.789169111934073</v>
+        <v>2.892471671635335</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0785862653435607</v>
+        <v>0.07750974116077219</v>
       </c>
       <c r="W74">
-        <v>0.2172693586319884</v>
+        <v>0.2175232030342899</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3143450613742428</v>
+        <v>0.3100389646430888</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2112242684315697</v>
+        <v>0.2131242684315696</v>
       </c>
       <c r="C75">
-        <v>-1521.674109906706</v>
+        <v>-1561.341707203915</v>
       </c>
       <c r="D75">
-        <v>668.2928900932935</v>
+        <v>660.7042927960846</v>
       </c>
       <c r="E75">
-        <v>801.9669999999999</v>
+        <v>834.0459999999996</v>
       </c>
       <c r="F75">
-        <v>2341.767</v>
+        <v>2373.846</v>
       </c>
       <c r="G75">
         <v>151.8</v>
@@ -7437,37 +7437,37 @@
         <v>171.2</v>
       </c>
       <c r="M75">
-        <v>552.1886585999999</v>
+        <v>559.7528867999999</v>
       </c>
       <c r="N75">
-        <v>-380.9886586</v>
+        <v>-388.5528868</v>
       </c>
       <c r="O75">
-        <v>-95.24716464999999</v>
+        <v>-97.13822169999999</v>
       </c>
       <c r="P75">
-        <v>-285.7414939499999</v>
+        <v>-291.4146651</v>
       </c>
       <c r="Q75">
-        <v>-50.04149394999996</v>
+        <v>-55.71466509999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1941938156168074</v>
+        <v>0.1999012700636077</v>
       </c>
       <c r="T75">
-        <v>2.892471671635335</v>
+        <v>3.003720582082849</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07750974116077219</v>
+        <v>0.07646231222616716</v>
       </c>
       <c r="W75">
-        <v>0.2175232030342899</v>
+        <v>0.2177701867770698</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3100389646430888</v>
+        <v>0.3058492489046686</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2131242684315696</v>
+        <v>0.2150242684315697</v>
       </c>
       <c r="C76">
-        <v>-1561.341707203915</v>
+        <v>-1600.83889945227</v>
       </c>
       <c r="D76">
-        <v>660.7042927960846</v>
+        <v>653.2861005477298</v>
       </c>
       <c r="E76">
-        <v>834.0459999999996</v>
+        <v>866.1249999999998</v>
       </c>
       <c r="F76">
-        <v>2373.846</v>
+        <v>2405.925</v>
       </c>
       <c r="G76">
         <v>151.8</v>
@@ -7519,37 +7519,37 @@
         <v>171.2</v>
       </c>
       <c r="M76">
-        <v>559.7528867999999</v>
+        <v>567.3171149999999</v>
       </c>
       <c r="N76">
-        <v>-388.5528868</v>
+        <v>-396.117115</v>
       </c>
       <c r="O76">
-        <v>-97.13822169999999</v>
+        <v>-99.02927874999999</v>
       </c>
       <c r="P76">
-        <v>-291.4146651</v>
+        <v>-297.08783625</v>
       </c>
       <c r="Q76">
-        <v>-55.71466509999999</v>
+        <v>-61.38783624999996</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1999012700636077</v>
+        <v>0.206065320866152</v>
       </c>
       <c r="T76">
-        <v>3.003720582082849</v>
+        <v>3.123869405366163</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07646231222616716</v>
+        <v>0.07544281472981826</v>
       </c>
       <c r="W76">
-        <v>0.2177701867770698</v>
+        <v>0.2180105842867089</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3058492489046686</v>
+        <v>0.301771258919273</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2150242684315697</v>
+        <v>0.2169242684315696</v>
       </c>
       <c r="C77">
-        <v>-1600.83889945227</v>
+        <v>-1640.171362695194</v>
       </c>
       <c r="D77">
-        <v>653.2861005477298</v>
+        <v>646.0326373048058</v>
       </c>
       <c r="E77">
-        <v>866.1249999999998</v>
+        <v>898.204</v>
       </c>
       <c r="F77">
-        <v>2405.925</v>
+        <v>2438.004</v>
       </c>
       <c r="G77">
         <v>151.8</v>
@@ -7601,37 +7601,37 @@
         <v>171.2</v>
       </c>
       <c r="M77">
-        <v>567.3171149999999</v>
+        <v>574.8813431999999</v>
       </c>
       <c r="N77">
-        <v>-396.117115</v>
+        <v>-403.6813432</v>
       </c>
       <c r="O77">
-        <v>-99.02927874999999</v>
+        <v>-100.9203358</v>
       </c>
       <c r="P77">
-        <v>-297.08783625</v>
+        <v>-302.7610074</v>
       </c>
       <c r="Q77">
-        <v>-61.38783624999996</v>
+        <v>-67.06100739999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.206065320866152</v>
+        <v>0.2127430425689083</v>
       </c>
       <c r="T77">
-        <v>3.123869405366163</v>
+        <v>3.254030630589753</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07544281472981826</v>
+        <v>0.07445014611495224</v>
       </c>
       <c r="W77">
-        <v>0.2180105842867089</v>
+        <v>0.2182446555460943</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.301771258919273</v>
+        <v>0.2978005844598089</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2169242684315696</v>
+        <v>0.2188242684315697</v>
       </c>
       <c r="C78">
-        <v>-1640.171362695194</v>
+        <v>-1679.344523658889</v>
       </c>
       <c r="D78">
-        <v>646.0326373048058</v>
+        <v>638.9384763411106</v>
       </c>
       <c r="E78">
-        <v>898.204</v>
+        <v>930.2829999999997</v>
       </c>
       <c r="F78">
-        <v>2438.004</v>
+        <v>2470.083</v>
       </c>
       <c r="G78">
         <v>151.8</v>
@@ -7683,37 +7683,37 @@
         <v>171.2</v>
       </c>
       <c r="M78">
-        <v>574.8813431999999</v>
+        <v>582.4455713999999</v>
       </c>
       <c r="N78">
-        <v>-403.6813432</v>
+        <v>-411.2455714</v>
       </c>
       <c r="O78">
-        <v>-100.9203358</v>
+        <v>-102.81139285</v>
       </c>
       <c r="P78">
-        <v>-302.7610074</v>
+        <v>-308.43417855</v>
       </c>
       <c r="Q78">
-        <v>-67.06100739999999</v>
+        <v>-72.73417854999997</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2127430425689083</v>
+        <v>0.2200014357240783</v>
       </c>
       <c r="T78">
-        <v>3.254030630589753</v>
+        <v>3.395510223224091</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07445014611495224</v>
+        <v>0.07348326110047233</v>
       </c>
       <c r="W78">
-        <v>0.2182446555460943</v>
+        <v>0.2184726470325086</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2978005844598089</v>
+        <v>0.2939330444018894</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2188242684315697</v>
+        <v>0.2207242684315696</v>
       </c>
       <c r="C79">
-        <v>-1679.344523658889</v>
+        <v>-1718.363573292557</v>
       </c>
       <c r="D79">
-        <v>638.9384763411106</v>
+        <v>631.9984267074431</v>
       </c>
       <c r="E79">
-        <v>930.2829999999997</v>
+        <v>962.3619999999999</v>
       </c>
       <c r="F79">
-        <v>2470.083</v>
+        <v>2502.162</v>
       </c>
       <c r="G79">
         <v>151.8</v>
@@ -7765,37 +7765,37 @@
         <v>171.2</v>
       </c>
       <c r="M79">
-        <v>582.4455713999999</v>
+        <v>590.0097996</v>
       </c>
       <c r="N79">
-        <v>-411.2455714</v>
+        <v>-418.8097996</v>
       </c>
       <c r="O79">
-        <v>-102.81139285</v>
+        <v>-104.7024499</v>
       </c>
       <c r="P79">
-        <v>-308.43417855</v>
+        <v>-314.1073497</v>
       </c>
       <c r="Q79">
-        <v>-72.73417854999997</v>
+        <v>-78.4073497</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2200014357240783</v>
+        <v>0.2279196828024455</v>
       </c>
       <c r="T79">
-        <v>3.395510223224091</v>
+        <v>3.549851597007003</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07348326110047233</v>
+        <v>0.07254116800944063</v>
       </c>
       <c r="W79">
-        <v>0.2184726470325086</v>
+        <v>0.2186947925833739</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2939330444018894</v>
+        <v>0.2901646720377625</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2207242684315696</v>
+        <v>0.2226242684315697</v>
       </c>
       <c r="C80">
-        <v>-1718.363573292557</v>
+        <v>-1757.233479435674</v>
       </c>
       <c r="D80">
-        <v>631.9984267074431</v>
+        <v>625.2075205643258</v>
       </c>
       <c r="E80">
-        <v>962.3619999999999</v>
+        <v>994.441</v>
       </c>
       <c r="F80">
-        <v>2502.162</v>
+        <v>2534.241</v>
       </c>
       <c r="G80">
         <v>151.8</v>
@@ -7847,37 +7847,37 @@
         <v>171.2</v>
       </c>
       <c r="M80">
-        <v>590.0097996</v>
+        <v>597.5740278000001</v>
       </c>
       <c r="N80">
-        <v>-418.8097996</v>
+        <v>-426.3740278000001</v>
       </c>
       <c r="O80">
-        <v>-104.7024499</v>
+        <v>-106.59350695</v>
       </c>
       <c r="P80">
-        <v>-314.1073497</v>
+        <v>-319.7805208500001</v>
       </c>
       <c r="Q80">
-        <v>-78.4073497</v>
+        <v>-84.08052085000008</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2279196828024455</v>
+        <v>0.236592048650181</v>
       </c>
       <c r="T80">
-        <v>3.549851597007003</v>
+        <v>3.718892149245433</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07254116800944063</v>
+        <v>0.07162292537640973</v>
       </c>
       <c r="W80">
-        <v>0.2186947925833739</v>
+        <v>0.2189113141962426</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2901646720377625</v>
+        <v>0.286491701505639</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2226242684315697</v>
+        <v>0.2245242684315697</v>
       </c>
       <c r="C81">
-        <v>-1757.233479435674</v>
+        <v>-1795.958998677279</v>
       </c>
       <c r="D81">
-        <v>625.2075205643258</v>
+        <v>618.5610013227207</v>
       </c>
       <c r="E81">
-        <v>994.441</v>
+        <v>1026.52</v>
       </c>
       <c r="F81">
-        <v>2534.241</v>
+        <v>2566.32</v>
       </c>
       <c r="G81">
         <v>151.8</v>
@@ -7929,37 +7929,37 @@
         <v>171.2</v>
       </c>
       <c r="M81">
-        <v>597.5740278000001</v>
+        <v>605.138256</v>
       </c>
       <c r="N81">
-        <v>-426.3740278000001</v>
+        <v>-433.938256</v>
       </c>
       <c r="O81">
-        <v>-106.59350695</v>
+        <v>-108.484564</v>
       </c>
       <c r="P81">
-        <v>-319.7805208500001</v>
+        <v>-325.453692</v>
       </c>
       <c r="Q81">
-        <v>-84.08052085000008</v>
+        <v>-89.753692</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.236592048650181</v>
+        <v>0.2461316510826901</v>
       </c>
       <c r="T81">
-        <v>3.718892149245433</v>
+        <v>3.904836756707704</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07162292537640973</v>
+        <v>0.07072763880920462</v>
       </c>
       <c r="W81">
-        <v>0.2189113141962426</v>
+        <v>0.2191224227687896</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.286491701505639</v>
+        <v>0.2829105552368185</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2245242684315697</v>
+        <v>0.2264242684315697</v>
       </c>
       <c r="C82">
-        <v>-1795.958998677279</v>
+        <v>-1834.544687466767</v>
       </c>
       <c r="D82">
-        <v>618.5610013227207</v>
+        <v>612.0543125332327</v>
       </c>
       <c r="E82">
-        <v>1026.52</v>
+        <v>1058.599</v>
       </c>
       <c r="F82">
-        <v>2566.32</v>
+        <v>2598.399</v>
       </c>
       <c r="G82">
         <v>151.8</v>
@@ -8011,37 +8011,37 @@
         <v>171.2</v>
       </c>
       <c r="M82">
-        <v>605.138256</v>
+        <v>612.7024842</v>
       </c>
       <c r="N82">
-        <v>-433.938256</v>
+        <v>-441.5024842</v>
       </c>
       <c r="O82">
-        <v>-108.484564</v>
+        <v>-110.37562105</v>
       </c>
       <c r="P82">
-        <v>-325.453692</v>
+        <v>-331.12686315</v>
       </c>
       <c r="Q82">
-        <v>-89.753692</v>
+        <v>-95.42686314999997</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2461316510826901</v>
+        <v>0.2566754221923053</v>
       </c>
       <c r="T82">
-        <v>3.904836756707704</v>
+        <v>4.110354480744951</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07072763880920462</v>
+        <v>0.06985445808316505</v>
       </c>
       <c r="W82">
-        <v>0.2191224227687896</v>
+        <v>0.2193283187839897</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2829105552368185</v>
+        <v>0.2794178323326603</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2264242684315697</v>
+        <v>0.2283242684315697</v>
       </c>
       <c r="C83">
-        <v>-1834.544687466767</v>
+        <v>-1872.994912530733</v>
       </c>
       <c r="D83">
-        <v>612.0543125332327</v>
+        <v>605.6830874692673</v>
       </c>
       <c r="E83">
-        <v>1058.599</v>
+        <v>1090.678</v>
       </c>
       <c r="F83">
-        <v>2598.399</v>
+        <v>2630.478</v>
       </c>
       <c r="G83">
         <v>151.8</v>
@@ -8093,37 +8093,37 @@
         <v>171.2</v>
       </c>
       <c r="M83">
-        <v>612.7024842</v>
+        <v>620.2667124000001</v>
       </c>
       <c r="N83">
-        <v>-441.5024842</v>
+        <v>-449.0667124000001</v>
       </c>
       <c r="O83">
-        <v>-110.37562105</v>
+        <v>-112.2666781</v>
       </c>
       <c r="P83">
-        <v>-331.12686315</v>
+        <v>-336.8000343</v>
       </c>
       <c r="Q83">
-        <v>-95.42686314999997</v>
+        <v>-101.1000343000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2566754221923053</v>
+        <v>0.2683907234252111</v>
       </c>
       <c r="T83">
-        <v>4.110354480744951</v>
+        <v>4.338707507453004</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06985445808316505</v>
+        <v>0.06900257444800449</v>
       </c>
       <c r="W83">
-        <v>0.2193283187839897</v>
+        <v>0.2195291929451605</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2794178323326603</v>
+        <v>0.276010297792018</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2283242684315697</v>
+        <v>0.2302242684315697</v>
       </c>
       <c r="C84">
-        <v>-1872.994912530733</v>
+        <v>-1911.313860645905</v>
       </c>
       <c r="D84">
-        <v>605.6830874692673</v>
+        <v>599.443139354095</v>
       </c>
       <c r="E84">
-        <v>1090.678</v>
+        <v>1122.757</v>
       </c>
       <c r="F84">
-        <v>2630.478</v>
+        <v>2662.557</v>
       </c>
       <c r="G84">
         <v>151.8</v>
@@ -8175,37 +8175,37 @@
         <v>171.2</v>
       </c>
       <c r="M84">
-        <v>620.2667124000001</v>
+        <v>627.8309406</v>
       </c>
       <c r="N84">
-        <v>-449.0667124000001</v>
+        <v>-456.6309406</v>
       </c>
       <c r="O84">
-        <v>-112.2666781</v>
+        <v>-114.15773515</v>
       </c>
       <c r="P84">
-        <v>-336.8000343</v>
+        <v>-342.47320545</v>
       </c>
       <c r="Q84">
-        <v>-101.1000343000001</v>
+        <v>-106.77320545</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2683907234252111</v>
+        <v>0.2814842953914001</v>
       </c>
       <c r="T84">
-        <v>4.338707507453004</v>
+        <v>4.593925596126711</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06900257444800449</v>
+        <v>0.06817121812935385</v>
       </c>
       <c r="W84">
-        <v>0.2195291929451605</v>
+        <v>0.2197252267650984</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.276010297792018</v>
+        <v>0.2726848725174154</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2302242684315697</v>
+        <v>0.2321242684315697</v>
       </c>
       <c r="C85">
-        <v>-1911.313860645905</v>
+        <v>-1949.505547814142</v>
       </c>
       <c r="D85">
-        <v>599.443139354095</v>
+        <v>593.3304521858583</v>
       </c>
       <c r="E85">
-        <v>1122.757</v>
+        <v>1154.836</v>
       </c>
       <c r="F85">
-        <v>2662.557</v>
+        <v>2694.636</v>
       </c>
       <c r="G85">
         <v>151.8</v>
@@ -8257,37 +8257,37 @@
         <v>171.2</v>
       </c>
       <c r="M85">
-        <v>627.8309406</v>
+        <v>635.3951688</v>
       </c>
       <c r="N85">
-        <v>-456.6309406</v>
+        <v>-464.1951688</v>
       </c>
       <c r="O85">
-        <v>-114.15773515</v>
+        <v>-116.0487922</v>
       </c>
       <c r="P85">
-        <v>-342.47320545</v>
+        <v>-348.1463766</v>
       </c>
       <c r="Q85">
-        <v>-106.77320545</v>
+        <v>-112.4463766</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2814842953914001</v>
+        <v>0.2962145638533626</v>
       </c>
       <c r="T85">
-        <v>4.593925596126711</v>
+        <v>4.881045945884632</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06817121812935385</v>
+        <v>0.0673596560087663</v>
       </c>
       <c r="W85">
-        <v>0.2197252267650984</v>
+        <v>0.2199165931131329</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2726848725174154</v>
+        <v>0.2694386240350652</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2321242684315696</v>
+        <v>0.2340242684315696</v>
       </c>
       <c r="C86">
-        <v>-1949.505547814141</v>
+        <v>-1987.573827881727</v>
       </c>
       <c r="D86">
-        <v>593.3304521858583</v>
+        <v>587.3411721182724</v>
       </c>
       <c r="E86">
-        <v>1154.836</v>
+        <v>1186.915</v>
       </c>
       <c r="F86">
-        <v>2694.636</v>
+        <v>2726.715</v>
       </c>
       <c r="G86">
         <v>151.8</v>
@@ -8339,37 +8339,37 @@
         <v>171.2</v>
       </c>
       <c r="M86">
-        <v>635.3951688</v>
+        <v>642.959397</v>
       </c>
       <c r="N86">
-        <v>-464.1951688</v>
+        <v>-471.759397</v>
       </c>
       <c r="O86">
-        <v>-116.0487922</v>
+        <v>-117.93984925</v>
       </c>
       <c r="P86">
-        <v>-348.1463766</v>
+        <v>-353.81954775</v>
       </c>
       <c r="Q86">
-        <v>-112.4463766</v>
+        <v>-118.11954775</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2962145638533625</v>
+        <v>0.3129088681102533</v>
       </c>
       <c r="T86">
-        <v>4.881045945884629</v>
+        <v>5.206449008943603</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0673596560087663</v>
+        <v>0.0665671894674867</v>
       </c>
       <c r="W86">
-        <v>0.2199165931131329</v>
+        <v>0.2201034567235666</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2694386240350652</v>
+        <v>0.2662687578699467</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2340242684315696</v>
+        <v>0.2359242684315697</v>
       </c>
       <c r="C87">
-        <v>-1987.573827881727</v>
+        <v>-2025.522400641853</v>
       </c>
       <c r="D87">
-        <v>587.3411721182724</v>
+        <v>581.4715993581468</v>
       </c>
       <c r="E87">
-        <v>1186.915</v>
+        <v>1218.994</v>
       </c>
       <c r="F87">
-        <v>2726.715</v>
+        <v>2758.794</v>
       </c>
       <c r="G87">
         <v>151.8</v>
@@ -8421,37 +8421,37 @@
         <v>171.2</v>
       </c>
       <c r="M87">
-        <v>642.959397</v>
+        <v>650.5236252</v>
       </c>
       <c r="N87">
-        <v>-471.759397</v>
+        <v>-479.3236252</v>
       </c>
       <c r="O87">
-        <v>-117.93984925</v>
+        <v>-119.8309063</v>
       </c>
       <c r="P87">
-        <v>-353.81954775</v>
+        <v>-359.4927189</v>
       </c>
       <c r="Q87">
-        <v>-118.11954775</v>
+        <v>-123.7927189</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3129088681102533</v>
+        <v>0.3319880729752714</v>
       </c>
       <c r="T87">
-        <v>5.206449008943603</v>
+        <v>5.578338223868147</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0665671894674867</v>
+        <v>0.06579315238065546</v>
       </c>
       <c r="W87">
-        <v>0.2201034567235666</v>
+        <v>0.2202859746686415</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2662687578699467</v>
+        <v>0.2631726095226218</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2359242684315697</v>
+        <v>0.2378242684315697</v>
       </c>
       <c r="C88">
-        <v>-2025.522400641853</v>
+        <v>-2063.35481945607</v>
       </c>
       <c r="D88">
-        <v>581.4715993581468</v>
+        <v>575.7181805439296</v>
       </c>
       <c r="E88">
-        <v>1218.994</v>
+        <v>1251.073</v>
       </c>
       <c r="F88">
-        <v>2758.794</v>
+        <v>2790.873</v>
       </c>
       <c r="G88">
         <v>151.8</v>
@@ -8503,37 +8503,37 @@
         <v>171.2</v>
       </c>
       <c r="M88">
-        <v>650.5236252</v>
+        <v>658.0878534</v>
       </c>
       <c r="N88">
-        <v>-479.3236252</v>
+        <v>-486.8878534</v>
       </c>
       <c r="O88">
-        <v>-119.8309063</v>
+        <v>-121.72196335</v>
       </c>
       <c r="P88">
-        <v>-359.4927189</v>
+        <v>-365.16589005</v>
       </c>
       <c r="Q88">
-        <v>-123.7927189</v>
+        <v>-129.46589005</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3319880729752714</v>
+        <v>0.3540025401272154</v>
       </c>
       <c r="T88">
-        <v>5.578338223868147</v>
+        <v>6.007441164165697</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06579315238065546</v>
+        <v>0.06503690924984333</v>
       </c>
       <c r="W88">
-        <v>0.2202859746686415</v>
+        <v>0.220464296798887</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2631726095226218</v>
+        <v>0.2601476369993733</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2378242684315697</v>
+        <v>0.2397242684315697</v>
       </c>
       <c r="C89">
-        <v>-2063.35481945607</v>
+        <v>-2101.074498427714</v>
       </c>
       <c r="D89">
-        <v>575.7181805439296</v>
+        <v>570.0775015722855</v>
       </c>
       <c r="E89">
-        <v>1251.073</v>
+        <v>1283.152</v>
       </c>
       <c r="F89">
-        <v>2790.873</v>
+        <v>2822.952</v>
       </c>
       <c r="G89">
         <v>151.8</v>
@@ -8585,37 +8585,37 @@
         <v>171.2</v>
       </c>
       <c r="M89">
-        <v>658.0878534</v>
+        <v>665.6520816</v>
       </c>
       <c r="N89">
-        <v>-486.8878534</v>
+        <v>-494.4520816</v>
       </c>
       <c r="O89">
-        <v>-121.72196335</v>
+        <v>-123.6130204</v>
       </c>
       <c r="P89">
-        <v>-365.16589005</v>
+        <v>-370.8390612</v>
       </c>
       <c r="Q89">
-        <v>-129.46589005</v>
+        <v>-135.1390612</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3540025401272154</v>
+        <v>0.3796860851378167</v>
       </c>
       <c r="T89">
-        <v>6.007441164165697</v>
+        <v>6.508061261179506</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06503690924984333</v>
+        <v>0.06429785346291329</v>
       </c>
       <c r="W89">
-        <v>0.220464296798887</v>
+        <v>0.2206385661534451</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2601476369993733</v>
+        <v>0.2571914138516531</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2397242684315697</v>
+        <v>0.2416242684315697</v>
       </c>
       <c r="C90">
-        <v>-2101.074498427714</v>
+        <v>-2138.684719157722</v>
       </c>
       <c r="D90">
-        <v>570.0775015722855</v>
+        <v>564.5462808422775</v>
       </c>
       <c r="E90">
-        <v>1283.152</v>
+        <v>1315.231</v>
       </c>
       <c r="F90">
-        <v>2822.952</v>
+        <v>2855.030999999999</v>
       </c>
       <c r="G90">
         <v>151.8</v>
@@ -8667,37 +8667,37 @@
         <v>171.2</v>
       </c>
       <c r="M90">
-        <v>665.6520816</v>
+        <v>673.2163097999999</v>
       </c>
       <c r="N90">
-        <v>-494.4520816</v>
+        <v>-502.0163097999999</v>
       </c>
       <c r="O90">
-        <v>-123.6130204</v>
+        <v>-125.50407745</v>
       </c>
       <c r="P90">
-        <v>-370.8390612</v>
+        <v>-376.5122323499999</v>
       </c>
       <c r="Q90">
-        <v>-135.1390612</v>
+        <v>-140.8122323499999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3796860851378167</v>
+        <v>0.410039365604891</v>
       </c>
       <c r="T90">
-        <v>6.508061261179506</v>
+        <v>7.099703194014007</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06429785346291329</v>
+        <v>0.06357540567119517</v>
       </c>
       <c r="W90">
-        <v>0.2206385661534451</v>
+        <v>0.2208089193427322</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2571914138516531</v>
+        <v>0.2543016226847807</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2416242684315697</v>
+        <v>0.2435242684315696</v>
       </c>
       <c r="C91">
-        <v>-2138.684719157722</v>
+        <v>-2176.188637110935</v>
       </c>
       <c r="D91">
-        <v>564.5462808422775</v>
+        <v>559.1213628890647</v>
       </c>
       <c r="E91">
-        <v>1315.231</v>
+        <v>1347.31</v>
       </c>
       <c r="F91">
-        <v>2855.030999999999</v>
+        <v>2887.11</v>
       </c>
       <c r="G91">
         <v>151.8</v>
@@ -8749,37 +8749,37 @@
         <v>171.2</v>
       </c>
       <c r="M91">
-        <v>673.2163097999999</v>
+        <v>680.780538</v>
       </c>
       <c r="N91">
-        <v>-502.0163097999999</v>
+        <v>-509.580538</v>
       </c>
       <c r="O91">
-        <v>-125.50407745</v>
+        <v>-127.3951345</v>
       </c>
       <c r="P91">
-        <v>-376.5122323499999</v>
+        <v>-382.1854035</v>
       </c>
       <c r="Q91">
-        <v>-140.8122323499999</v>
+        <v>-146.4854035</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.410039365604891</v>
+        <v>0.4464633021653801</v>
       </c>
       <c r="T91">
-        <v>7.099703194014007</v>
+        <v>7.809673513415408</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06357540567119517</v>
+        <v>0.06286901227484855</v>
       </c>
       <c r="W91">
-        <v>0.2208089193427322</v>
+        <v>0.2209754869055907</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2543016226847807</v>
+        <v>0.2514760490993941</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2435242684315696</v>
+        <v>0.2454242684315696</v>
       </c>
       <c r="C92">
-        <v>-2176.188637110935</v>
+        <v>-2213.589287618841</v>
       </c>
       <c r="D92">
-        <v>559.1213628890647</v>
+        <v>553.7997123811585</v>
       </c>
       <c r="E92">
-        <v>1347.31</v>
+        <v>1379.389</v>
       </c>
       <c r="F92">
-        <v>2887.11</v>
+        <v>2919.189</v>
       </c>
       <c r="G92">
         <v>151.8</v>
@@ -8831,37 +8831,37 @@
         <v>171.2</v>
       </c>
       <c r="M92">
-        <v>680.780538</v>
+        <v>688.3447662</v>
       </c>
       <c r="N92">
-        <v>-509.580538</v>
+        <v>-517.1447662</v>
       </c>
       <c r="O92">
-        <v>-127.3951345</v>
+        <v>-129.28619155</v>
       </c>
       <c r="P92">
-        <v>-382.1854035</v>
+        <v>-387.85857465</v>
       </c>
       <c r="Q92">
-        <v>-146.4854035</v>
+        <v>-152.15857465</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4464633021653801</v>
+        <v>0.4909814468504223</v>
       </c>
       <c r="T92">
-        <v>7.809673513415408</v>
+        <v>8.677415014906009</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06286901227484855</v>
+        <v>0.06217814400809197</v>
       </c>
       <c r="W92">
-        <v>0.2209754869055907</v>
+        <v>0.2211383936428919</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2514760490993941</v>
+        <v>0.2487125760323678</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2454242684315696</v>
+        <v>0.2473242684315697</v>
       </c>
       <c r="C93">
-        <v>-2213.589287618841</v>
+        <v>-2250.889591542748</v>
       </c>
       <c r="D93">
-        <v>553.7997123811585</v>
+        <v>548.5784084572516</v>
       </c>
       <c r="E93">
-        <v>1379.389</v>
+        <v>1411.468</v>
       </c>
       <c r="F93">
-        <v>2919.189</v>
+        <v>2951.268</v>
       </c>
       <c r="G93">
         <v>151.8</v>
@@ -8913,37 +8913,37 @@
         <v>171.2</v>
       </c>
       <c r="M93">
-        <v>688.3447662</v>
+        <v>695.9089944</v>
       </c>
       <c r="N93">
-        <v>-517.1447662</v>
+        <v>-524.7089943999999</v>
       </c>
       <c r="O93">
-        <v>-129.28619155</v>
+        <v>-131.1772486</v>
       </c>
       <c r="P93">
-        <v>-387.85857465</v>
+        <v>-393.5317458</v>
       </c>
       <c r="Q93">
-        <v>-152.15857465</v>
+        <v>-157.8317458</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4909814468504223</v>
+        <v>0.5466291277067252</v>
       </c>
       <c r="T93">
-        <v>8.677415014906009</v>
+        <v>9.762091891769265</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06217814400809197</v>
+        <v>0.06150229461669967</v>
       </c>
       <c r="W93">
-        <v>0.2211383936428919</v>
+        <v>0.2212977589293822</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2487125760323678</v>
+        <v>0.2460091784667987</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2473242684315697</v>
+        <v>0.2492242684315697</v>
       </c>
       <c r="C94">
-        <v>-2250.889591542748</v>
+        <v>-2288.092360619589</v>
       </c>
       <c r="D94">
-        <v>548.5784084572516</v>
+        <v>543.4546393804102</v>
       </c>
       <c r="E94">
-        <v>1411.468</v>
+        <v>1443.547</v>
       </c>
       <c r="F94">
-        <v>2951.268</v>
+        <v>2983.347</v>
       </c>
       <c r="G94">
         <v>151.8</v>
@@ -8995,37 +8995,37 @@
         <v>171.2</v>
       </c>
       <c r="M94">
-        <v>695.9089944</v>
+        <v>703.4732226</v>
       </c>
       <c r="N94">
-        <v>-524.7089943999999</v>
+        <v>-532.2732226000001</v>
       </c>
       <c r="O94">
-        <v>-131.1772486</v>
+        <v>-133.06830565</v>
       </c>
       <c r="P94">
-        <v>-393.5317458</v>
+        <v>-399.20491695</v>
       </c>
       <c r="Q94">
-        <v>-157.8317458</v>
+        <v>-163.5049169500001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5466291277067252</v>
+        <v>0.6181761459505432</v>
       </c>
       <c r="T94">
-        <v>9.762091891769265</v>
+        <v>11.1566764477363</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06150229461669967</v>
+        <v>0.06084097962082118</v>
       </c>
       <c r="W94">
-        <v>0.2212977589293822</v>
+        <v>0.2214536970054104</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2460091784667987</v>
+        <v>0.2433639184832846</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2492242684315697</v>
+        <v>0.2511242684315697</v>
       </c>
       <c r="C95">
-        <v>-2288.092360619589</v>
+        <v>-2325.200302510922</v>
       </c>
       <c r="D95">
-        <v>543.4546393804102</v>
+        <v>538.4256974890773</v>
       </c>
       <c r="E95">
-        <v>1443.547</v>
+        <v>1475.626</v>
       </c>
       <c r="F95">
-        <v>2983.347</v>
+        <v>3015.426</v>
       </c>
       <c r="G95">
         <v>151.8</v>
@@ -9077,37 +9077,37 @@
         <v>171.2</v>
       </c>
       <c r="M95">
-        <v>703.4732226</v>
+        <v>711.0374508</v>
       </c>
       <c r="N95">
-        <v>-532.2732226000001</v>
+        <v>-539.8374507999999</v>
       </c>
       <c r="O95">
-        <v>-133.06830565</v>
+        <v>-134.9593627</v>
       </c>
       <c r="P95">
-        <v>-399.20491695</v>
+        <v>-404.8780881</v>
       </c>
       <c r="Q95">
-        <v>-163.5049169500001</v>
+        <v>-169.1780881</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6181761459505432</v>
+        <v>0.713572170275634</v>
       </c>
       <c r="T95">
-        <v>11.1566764477363</v>
+        <v>13.01612252235902</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06084097962082118</v>
+        <v>0.06019373515676989</v>
       </c>
       <c r="W95">
-        <v>0.2214536970054104</v>
+        <v>0.2216063172500337</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2433639184832846</v>
+        <v>0.2407749406270796</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2511242684315697</v>
+        <v>0.2530242684315697</v>
       </c>
       <c r="C96">
-        <v>-2325.200302510922</v>
+        <v>-2362.216025574163</v>
       </c>
       <c r="D96">
-        <v>538.4256974890773</v>
+        <v>533.488974425837</v>
       </c>
       <c r="E96">
-        <v>1475.626</v>
+        <v>1507.705</v>
       </c>
       <c r="F96">
-        <v>3015.426</v>
+        <v>3047.505</v>
       </c>
       <c r="G96">
         <v>151.8</v>
@@ -9159,37 +9159,37 @@
         <v>171.2</v>
       </c>
       <c r="M96">
-        <v>711.0374508</v>
+        <v>718.601679</v>
       </c>
       <c r="N96">
-        <v>-539.8374507999999</v>
+        <v>-547.4016790000001</v>
       </c>
       <c r="O96">
-        <v>-134.9593627</v>
+        <v>-136.85041975</v>
       </c>
       <c r="P96">
-        <v>-404.8780881</v>
+        <v>-410.55125925</v>
       </c>
       <c r="Q96">
-        <v>-169.1780881</v>
+        <v>-174.8512592500001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.713572170275634</v>
+        <v>0.8471266043307611</v>
       </c>
       <c r="T96">
-        <v>13.01612252235902</v>
+        <v>15.61934702683084</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06019373515676989</v>
+        <v>0.05956011689196178</v>
       </c>
       <c r="W96">
-        <v>0.2216063172500337</v>
+        <v>0.2217557244368754</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2407749406270796</v>
+        <v>0.238240467567847</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2530242684315697</v>
+        <v>0.2549242684315697</v>
       </c>
       <c r="C97">
-        <v>-2362.216025574163</v>
+        <v>-2399.142043373729</v>
       </c>
       <c r="D97">
-        <v>533.488974425837</v>
+        <v>528.6419566262707</v>
       </c>
       <c r="E97">
-        <v>1507.705</v>
+        <v>1539.784</v>
       </c>
       <c r="F97">
-        <v>3047.505</v>
+        <v>3079.584</v>
       </c>
       <c r="G97">
         <v>151.8</v>
@@ -9241,37 +9241,37 @@
         <v>171.2</v>
       </c>
       <c r="M97">
-        <v>718.601679</v>
+        <v>726.1659072</v>
       </c>
       <c r="N97">
-        <v>-547.4016790000001</v>
+        <v>-554.9659071999999</v>
       </c>
       <c r="O97">
-        <v>-136.85041975</v>
+        <v>-138.7414768</v>
       </c>
       <c r="P97">
-        <v>-410.55125925</v>
+        <v>-416.2244304</v>
       </c>
       <c r="Q97">
-        <v>-174.8512592500001</v>
+        <v>-180.5244304</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8471266043307611</v>
+        <v>1.047458255413452</v>
       </c>
       <c r="T97">
-        <v>15.61934702683084</v>
+        <v>19.52418378353855</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05956011689196178</v>
+        <v>0.05893969900767052</v>
       </c>
       <c r="W97">
-        <v>0.2217557244368754</v>
+        <v>0.2219020189739913</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.238240467567847</v>
+        <v>0.2357587960306822</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2549242684315697</v>
+        <v>0.2568242684315697</v>
       </c>
       <c r="C98">
-        <v>-2399.142043373728</v>
+        <v>-2435.980778948482</v>
       </c>
       <c r="D98">
-        <v>528.6419566262707</v>
+        <v>523.8822210515178</v>
       </c>
       <c r="E98">
-        <v>1539.783999999999</v>
+        <v>1571.863</v>
       </c>
       <c r="F98">
-        <v>3079.583999999999</v>
+        <v>3111.663</v>
       </c>
       <c r="G98">
         <v>151.8</v>
@@ -9323,37 +9323,37 @@
         <v>171.2</v>
       </c>
       <c r="M98">
-        <v>726.1659071999999</v>
+        <v>733.7301353999999</v>
       </c>
       <c r="N98">
-        <v>-554.9659071999999</v>
+        <v>-562.5301353999998</v>
       </c>
       <c r="O98">
-        <v>-138.7414768</v>
+        <v>-140.63253385</v>
       </c>
       <c r="P98">
-        <v>-416.2244304</v>
+        <v>-421.8976015499999</v>
       </c>
       <c r="Q98">
-        <v>-180.5244304</v>
+        <v>-186.1976015499999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.047458255413449</v>
+        <v>1.381344340551266</v>
       </c>
       <c r="T98">
-        <v>19.5241837835385</v>
+        <v>26.032245044718</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05893969900767052</v>
+        <v>0.05833207324470484</v>
       </c>
       <c r="W98">
-        <v>0.2219020189739913</v>
+        <v>0.2220452971288986</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2357587960306821</v>
+        <v>0.2333282929788194</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2568242684315697</v>
+        <v>0.2587242684315696</v>
       </c>
       <c r="C99">
-        <v>-2435.980778948482</v>
+        <v>-2472.734568850685</v>
       </c>
       <c r="D99">
-        <v>523.8822210515178</v>
+        <v>519.2074311493151</v>
       </c>
       <c r="E99">
-        <v>1571.863</v>
+        <v>1603.942</v>
       </c>
       <c r="F99">
-        <v>3111.663</v>
+        <v>3143.742</v>
       </c>
       <c r="G99">
         <v>151.8</v>
@@ -9405,37 +9405,37 @@
         <v>171.2</v>
       </c>
       <c r="M99">
-        <v>733.7301353999999</v>
+        <v>741.2943636</v>
       </c>
       <c r="N99">
-        <v>-562.5301353999998</v>
+        <v>-570.0943636</v>
       </c>
       <c r="O99">
-        <v>-140.63253385</v>
+        <v>-142.5235909</v>
       </c>
       <c r="P99">
-        <v>-421.8976015499999</v>
+        <v>-427.5707727</v>
       </c>
       <c r="Q99">
-        <v>-186.1976015499999</v>
+        <v>-191.8707727</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.381344340551266</v>
+        <v>2.049116510826898</v>
       </c>
       <c r="T99">
-        <v>26.032245044718</v>
+        <v>39.048367567077</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05833207324470484</v>
+        <v>0.05773684800751397</v>
       </c>
       <c r="W99">
-        <v>0.2220452971288986</v>
+        <v>0.2221856512398282</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2333282929788194</v>
+        <v>0.230947392030056</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2587242684315696</v>
+        <v>0.2606242684315697</v>
       </c>
       <c r="C100">
-        <v>-2472.734568850685</v>
+        <v>-2509.405666970632</v>
       </c>
       <c r="D100">
-        <v>519.2074311493151</v>
+        <v>514.6153330293673</v>
       </c>
       <c r="E100">
-        <v>1603.942</v>
+        <v>1636.021</v>
       </c>
       <c r="F100">
-        <v>3143.742</v>
+        <v>3175.820999999999</v>
       </c>
       <c r="G100">
         <v>151.8</v>
@@ -9487,37 +9487,37 @@
         <v>171.2</v>
       </c>
       <c r="M100">
-        <v>741.2943636</v>
+        <v>748.8585917999999</v>
       </c>
       <c r="N100">
-        <v>-570.0943636</v>
+        <v>-577.6585917999998</v>
       </c>
       <c r="O100">
-        <v>-142.5235909</v>
+        <v>-144.41464795</v>
       </c>
       <c r="P100">
-        <v>-427.5707727</v>
+        <v>-433.2439438499999</v>
       </c>
       <c r="Q100">
-        <v>-191.8707727</v>
+        <v>-197.5439438499999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.049116510826898</v>
+        <v>4.052433021653797</v>
       </c>
       <c r="T100">
-        <v>39.048367567077</v>
+        <v>78.096735134154</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05773684800751397</v>
+        <v>0.0571536475225896</v>
       </c>
       <c r="W100">
-        <v>0.2221856512398282</v>
+        <v>0.2223231699141734</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.230947392030056</v>
+        <v>0.2286145900903584</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2606242684315697</v>
-      </c>
-      <c r="C101">
-        <v>-2509.405666970632</v>
-      </c>
-      <c r="D101">
-        <v>514.6153330293673</v>
-      </c>
-      <c r="E101">
-        <v>1636.021</v>
-      </c>
-      <c r="F101">
-        <v>3175.820999999999</v>
-      </c>
-      <c r="G101">
-        <v>151.8</v>
-      </c>
-      <c r="H101">
-        <v>1668.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>406.9</v>
-      </c>
-      <c r="K101">
-        <v>235.7</v>
-      </c>
-      <c r="L101">
-        <v>171.2</v>
-      </c>
-      <c r="M101">
-        <v>748.8585917999999</v>
-      </c>
-      <c r="N101">
-        <v>-577.6585917999998</v>
-      </c>
-      <c r="O101">
-        <v>-144.41464795</v>
-      </c>
-      <c r="P101">
-        <v>-433.2439438499999</v>
-      </c>
-      <c r="Q101">
-        <v>-197.5439438499999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.052433021653797</v>
-      </c>
-      <c r="T101">
-        <v>78.096735134154</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0571536475225896</v>
-      </c>
-      <c r="W101">
-        <v>0.2223231699141734</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2286145900903584</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
